--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,55 +672,56 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2596274</v>
+        <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>99017</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219795</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442283</v>
+        <v>442331</v>
       </c>
       <c r="R2" t="n">
-        <v>7027836</v>
+        <v>7027586</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,73 +771,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4041960</v>
+        <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>106229</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442283</v>
+        <v>442433</v>
       </c>
       <c r="R3" t="n">
-        <v>7027836</v>
+        <v>7027808</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,78 +883,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574543</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55633849</v>
+        <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442283</v>
+        <v>442274</v>
       </c>
       <c r="R4" t="n">
-        <v>7027836</v>
+        <v>7027529</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,73 +995,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5168927</v>
+        <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>98137</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222741</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442283</v>
+        <v>442273</v>
       </c>
       <c r="R5" t="n">
-        <v>7027836</v>
+        <v>7027521</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,17 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,26 +1107,6201 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574571</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135574586</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>442348</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7027563</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574586</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135574589</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>442356</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7027575</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574589</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135574591</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>442368</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7027605</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574591</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135574594</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>442357</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7027656</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574594</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135574597</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>442378</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7027707</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574597</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135574609</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>442384</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027743</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574609</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135574620</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>442430</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7027615</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574620</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135574581</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>442302</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7027506</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574581</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135574623</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>442445</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7027645</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574623</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135574565</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92320</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>442271</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7027560</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574565</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135574562</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>442280</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7027559</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574562</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135574545</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93307</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>442440</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7027853</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574545</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135574538</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>442449</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7027722</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574538</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135574539</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>442445</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7027731</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574539</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135574540</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>442421</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7027753</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574540</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135574541</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>442414</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7027802</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574541</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135574542</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>442437</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7027801</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574542</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135574544</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>442430</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7027816</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574544</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135574550</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>442350</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7027791</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574550</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135574551</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>442295</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7027775</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574551</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135574553</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>442327</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7027590</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574553</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135574556</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>442329</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7027573</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574556</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135574558</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>442329</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7027569</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574558</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135574560</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>442311</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7027581</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574560</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135574561</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>442291</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7027577</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574561</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135574575</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>442296</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7027551</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574575</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135574580</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>442295</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7027519</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574580</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135574585</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>442348</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7027560</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574585</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135574587</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>442355</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7027577</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574587</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135574590</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>442386</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7027567</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574590</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135574593</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>442362</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7027657</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574593</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135574601</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>442387</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574601</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135574605</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>442416</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7027567</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574605</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135574608</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>442410</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7027707</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574608</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135574610</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>442382</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7027768</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574610</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135574611</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>442414</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7027804</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574611</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135574612</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>442425</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7027761</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574612</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135574616</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>442455</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7027671</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574616</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135574617</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>442432</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7027650</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574617</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135574625</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>442465</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7027665</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574625</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135574626</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>442550</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7027681</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574626</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135574627</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>442492</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7027713</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574627</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135574628</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>442502</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7027719</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574628</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2596274</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Lisbeth Berntsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2596274</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135574548</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7027839</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574548</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135574614</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>442464</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7027693</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574614</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135574549</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574549</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4041960</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4041960</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135574569</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99222</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7027534</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574569</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>55633849</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55633849</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135574547</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>442418</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7027847</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574547</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5168927</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5168927</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135574586</v>
       </c>
       <c r="B6" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135574589</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135574591</v>
       </c>
       <c r="B8" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135574594</v>
       </c>
       <c r="B9" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135574597</v>
       </c>
       <c r="B10" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135574609</v>
       </c>
       <c r="B11" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135574620</v>
       </c>
       <c r="B12" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135574581</v>
       </c>
       <c r="B13" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135574623</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135574565</v>
       </c>
       <c r="B15" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135574562</v>
       </c>
       <c r="B16" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135574545</v>
       </c>
       <c r="B17" t="n">
-        <v>93307</v>
+        <v>93349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135574538</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>135574539</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135574540</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135574541</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>135574542</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>135574544</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>135574550</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>135574551</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>135574553</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135574556</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>135574558</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>135574560</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>135574561</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135574575</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>135574580</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>135574585</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>135574587</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>135574590</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>135574593</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>135574601</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>135574605</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>135574608</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>135574610</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135574611</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>135574612</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135574616</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>135574617</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>135574625</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>135574626</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>135574627</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>135574628</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6216,49 +6216,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2596274</v>
+        <v>135635857</v>
       </c>
       <c r="B49" t="n">
-        <v>99017</v>
+        <v>58141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219795</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442283</v>
+        <v>442366</v>
       </c>
       <c r="R49" t="n">
-        <v>7027836</v>
+        <v>7027641</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6285,17 +6293,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6306,36 +6309,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
+          <t>https://artportalen.se/Sighting/135635857</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574548</v>
+        <v>2596274</v>
       </c>
       <c r="B50" t="n">
-        <v>99197</v>
+        <v>99017</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6343,37 +6341,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442411</v>
+        <v>442283</v>
       </c>
       <c r="R50" t="n">
-        <v>7027839</v>
+        <v>7027836</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6397,22 +6399,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6423,31 +6420,36 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
+          <t>https://artportalen.se/Sighting/2596274</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574614</v>
+        <v>135574548</v>
       </c>
       <c r="B51" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6479,10 +6481,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442464</v>
+        <v>442411</v>
       </c>
       <c r="R51" t="n">
-        <v>7027693</v>
+        <v>7027839</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6514,7 +6516,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6524,7 +6526,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6550,16 +6552,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
+          <t>https://artportalen.se/Sighting/135574548</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574549</v>
+        <v>135574614</v>
       </c>
       <c r="B52" t="n">
-        <v>99219</v>
+        <v>99244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6567,21 +6569,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6591,10 +6593,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442411</v>
+        <v>442464</v>
       </c>
       <c r="R52" t="n">
-        <v>7027836</v>
+        <v>7027693</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6626,7 +6628,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6636,7 +6638,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6662,16 +6664,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
+          <t>https://artportalen.se/Sighting/135574614</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4041960</v>
+        <v>135574549</v>
       </c>
       <c r="B53" t="n">
-        <v>106229</v>
+        <v>99266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6679,41 +6681,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442283</v>
+        <v>442411</v>
       </c>
       <c r="R53" t="n">
         <v>7027836</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6737,17 +6735,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6758,36 +6761,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
+          <t>https://artportalen.se/Sighting/135574549</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574569</v>
+        <v>4041960</v>
       </c>
       <c r="B54" t="n">
-        <v>99222</v>
+        <v>106229</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6795,37 +6793,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222118</v>
+        <v>221725</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>442283</v>
       </c>
       <c r="R54" t="n">
-        <v>7027534</v>
+        <v>7027836</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6849,22 +6851,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6875,31 +6872,36 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
+          <t>https://artportalen.se/Sighting/4041960</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55633849</v>
+        <v>135574569</v>
       </c>
       <c r="B55" t="n">
-        <v>101326</v>
+        <v>99269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6907,46 +6909,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>222118</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>442283</v>
       </c>
       <c r="R55" t="n">
-        <v>7027836</v>
+        <v>7027534</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6970,17 +6963,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6991,36 +6989,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
+          <t>https://artportalen.se/Sighting/135574569</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135574547</v>
+        <v>55633849</v>
       </c>
       <c r="B56" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7045,20 +7038,29 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442418</v>
+        <v>442283</v>
       </c>
       <c r="R56" t="n">
-        <v>7027847</v>
+        <v>7027836</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7082,22 +7084,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7108,31 +7105,36 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
+          <t>https://artportalen.se/Sighting/55633849</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5168927</v>
+        <v>135574547</v>
       </c>
       <c r="B57" t="n">
-        <v>98137</v>
+        <v>101451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,41 +7142,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442283</v>
+        <v>442418</v>
       </c>
       <c r="R57" t="n">
-        <v>7027836</v>
+        <v>7027847</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7198,17 +7196,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7219,25 +7222,136 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574547</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5168927</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5168927</t>
         </is>
@@ -7301,6 +7415,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135574586</v>
       </c>
       <c r="B6" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135574589</v>
       </c>
       <c r="B7" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135574591</v>
       </c>
       <c r="B8" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135574594</v>
       </c>
       <c r="B9" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135574597</v>
       </c>
       <c r="B10" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135574609</v>
       </c>
       <c r="B11" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135574620</v>
       </c>
       <c r="B12" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135574581</v>
       </c>
       <c r="B13" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135574623</v>
       </c>
       <c r="B14" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135574565</v>
       </c>
       <c r="B15" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135574562</v>
       </c>
       <c r="B16" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135574545</v>
       </c>
       <c r="B17" t="n">
-        <v>93349</v>
+        <v>93376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>135574548</v>
       </c>
       <c r="B51" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>135574614</v>
       </c>
       <c r="B52" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>135574549</v>
       </c>
       <c r="B53" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>135574569</v>
       </c>
       <c r="B55" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>135574547</v>
       </c>
       <c r="B57" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135574586</v>
       </c>
       <c r="B6" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135574589</v>
       </c>
       <c r="B7" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135574591</v>
       </c>
       <c r="B8" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135574594</v>
       </c>
       <c r="B9" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135574597</v>
       </c>
       <c r="B10" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135574609</v>
       </c>
       <c r="B11" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135574620</v>
       </c>
       <c r="B12" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135574581</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135574623</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135574565</v>
       </c>
       <c r="B16" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96489</v>
+        <v>96491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96489</v>
+        <v>96491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135574562</v>
       </c>
       <c r="B23" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91580</v>
+        <v>91582</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>135574545</v>
       </c>
       <c r="B25" t="n">
-        <v>93381</v>
+        <v>93383</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93381</v>
+        <v>93383</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93381</v>
+        <v>93383</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93381</v>
+        <v>93383</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135574548</v>
       </c>
       <c r="B73" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135574614</v>
       </c>
       <c r="B74" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>135574549</v>
       </c>
       <c r="B77" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>135574569</v>
       </c>
       <c r="B90" t="n">
-        <v>99301</v>
+        <v>99303</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100299</v>
+        <v>100301</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135574547</v>
       </c>
       <c r="B95" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574538</v>
+        <v>135574556</v>
       </c>
       <c r="B37" t="n">
         <v>57980</v>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442449</v>
+        <v>442329</v>
       </c>
       <c r="R37" t="n">
-        <v>7027722</v>
+        <v>7027573</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574538</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574539</v>
+        <v>135851785</v>
       </c>
       <c r="B38" t="n">
         <v>57980</v>
@@ -4772,24 +4772,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442445</v>
+        <v>442360</v>
       </c>
       <c r="R38" t="n">
-        <v>7027731</v>
+        <v>7027581</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4813,27 +4808,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,24 +4838,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574539</t>
+          <t>https://artportalen.se/Sighting/135851785</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574540</v>
+        <v>135851790</v>
       </c>
       <c r="B39" t="n">
         <v>57980</v>
@@ -4894,24 +4884,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442421</v>
+        <v>442323</v>
       </c>
       <c r="R39" t="n">
-        <v>7027753</v>
+        <v>7027596</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4935,27 +4928,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4970,24 +4963,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574540</t>
+          <t>https://artportalen.se/Sighting/135851790</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574541</v>
+        <v>135851813</v>
       </c>
       <c r="B40" t="n">
         <v>57980</v>
@@ -5016,24 +5009,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442414</v>
+        <v>442444</v>
       </c>
       <c r="R40" t="n">
-        <v>7027802</v>
+        <v>7027735</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5057,27 +5053,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,27 +5088,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574541</t>
+          <t>https://artportalen.se/Sighting/135851813</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574542</v>
+        <v>135635857</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5120,27 +5116,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5149,13 +5152,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442437</v>
+        <v>442366</v>
       </c>
       <c r="R41" t="n">
-        <v>7027801</v>
+        <v>7027641</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,24 +5185,9 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5225,59 +5213,58 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574542</t>
+          <t>https://artportalen.se/Sighting/135635857</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574544</v>
+        <v>2596274</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>99017</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442430</v>
+        <v>442283</v>
       </c>
       <c r="R42" t="n">
-        <v>7027816</v>
+        <v>7027836</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5301,27 +5288,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5332,74 +5309,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574544</t>
+          <t>https://artportalen.se/Sighting/2596274</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574550</v>
+        <v>135574548</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>99278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442350</v>
+        <v>442411</v>
       </c>
       <c r="R43" t="n">
-        <v>7027791</v>
+        <v>7027839</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5428,7 +5405,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5438,12 +5415,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,38 +5441,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574550</t>
+          <t>https://artportalen.se/Sighting/135574548</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574551</v>
+        <v>135574614</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>99278</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5510,10 +5482,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442295</v>
+        <v>442464</v>
       </c>
       <c r="R44" t="n">
-        <v>7027775</v>
+        <v>7027693</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5545,7 +5517,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5555,12 +5527,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5586,58 +5553,62 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574551</t>
+          <t>https://artportalen.se/Sighting/135574614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574553</v>
+        <v>135851773</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>99278</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442327</v>
+        <v>442469</v>
       </c>
       <c r="R45" t="n">
-        <v>7027590</v>
+        <v>7027704</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5661,27 +5632,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,76 +5656,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574553</t>
+          <t>https://artportalen.se/Sighting/135851773</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574556</v>
+        <v>135851816</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>99278</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442329</v>
+        <v>442473</v>
       </c>
       <c r="R46" t="n">
-        <v>7027573</v>
+        <v>7027780</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5783,34 +5745,29 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5818,67 +5775,62 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135851816</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574558</v>
+        <v>135574549</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442329</v>
+        <v>442411</v>
       </c>
       <c r="R47" t="n">
-        <v>7027569</v>
+        <v>7027836</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5910,7 +5862,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5920,12 +5872,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5951,59 +5898,62 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574558</t>
+          <t>https://artportalen.se/Sighting/135574549</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574560</v>
+        <v>135851772</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442311</v>
+        <v>442473</v>
       </c>
       <c r="R48" t="n">
-        <v>7027581</v>
+        <v>7027706</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6027,27 +5977,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6056,76 +6001,72 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574560</t>
+          <t>https://artportalen.se/Sighting/135851772</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574561</v>
+        <v>135851793</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442291</v>
+        <v>442287</v>
       </c>
       <c r="R49" t="n">
-        <v>7027577</v>
+        <v>7027599</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,27 +6090,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6184,70 +6120,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574561</t>
+          <t>https://artportalen.se/Sighting/135851793</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574575</v>
+        <v>135851800</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442296</v>
+        <v>442247</v>
       </c>
       <c r="R50" t="n">
-        <v>7027551</v>
+        <v>7027546</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,27 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6306,69 +6232,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574575</t>
+          <t>https://artportalen.se/Sighting/135851800</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574580</v>
+        <v>135851804</v>
       </c>
       <c r="B51" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442295</v>
+        <v>442275</v>
       </c>
       <c r="R51" t="n">
-        <v>7027519</v>
+        <v>7027599</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6392,27 +6314,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,69 +6344,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574580</t>
+          <t>https://artportalen.se/Sighting/135851804</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574585</v>
+        <v>135851814</v>
       </c>
       <c r="B52" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442348</v>
+        <v>442453</v>
       </c>
       <c r="R52" t="n">
-        <v>7027560</v>
+        <v>7027747</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6513,27 +6426,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,70 +6456,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574585</t>
+          <t>https://artportalen.se/Sighting/135851814</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574587</v>
+        <v>135851815</v>
       </c>
       <c r="B53" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442355</v>
+        <v>442471</v>
       </c>
       <c r="R53" t="n">
-        <v>7027577</v>
+        <v>7027763</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6635,27 +6538,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6670,70 +6568,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574587</t>
+          <t>https://artportalen.se/Sighting/135851815</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574590</v>
+        <v>135851774</v>
       </c>
       <c r="B54" t="n">
-        <v>57980</v>
+        <v>108364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442386</v>
+        <v>442467</v>
       </c>
       <c r="R54" t="n">
-        <v>7027567</v>
+        <v>7027703</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6757,27 +6650,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6792,65 +6680,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574590</t>
+          <t>https://artportalen.se/Sighting/135851774</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574593</v>
+        <v>4041960</v>
       </c>
       <c r="B55" t="n">
-        <v>57980</v>
+        <v>106229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442362</v>
+        <v>442283</v>
       </c>
       <c r="R55" t="n">
-        <v>7027657</v>
+        <v>7027836</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6874,27 +6766,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6905,74 +6787,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574593</t>
+          <t>https://artportalen.se/Sighting/4041960</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135574601</v>
+        <v>135851789</v>
       </c>
       <c r="B56" t="n">
-        <v>57980</v>
+        <v>106398</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442387</v>
+        <v>442341</v>
       </c>
       <c r="R56" t="n">
-        <v>7027641</v>
+        <v>7027597</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,27 +6878,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7031,65 +6908,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574601</t>
+          <t>https://artportalen.se/Sighting/135851789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135574605</v>
+        <v>135851806</v>
       </c>
       <c r="B57" t="n">
-        <v>57980</v>
+        <v>99298</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442416</v>
+        <v>442315</v>
       </c>
       <c r="R57" t="n">
-        <v>7027567</v>
+        <v>7027602</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,27 +6990,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7148,70 +7020,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574605</t>
+          <t>https://artportalen.se/Sighting/135851806</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135574608</v>
+        <v>135851807</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>99298</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442410</v>
+        <v>442368</v>
       </c>
       <c r="R58" t="n">
-        <v>7027707</v>
+        <v>7027641</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7235,27 +7102,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7270,65 +7132,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574608</t>
+          <t>https://artportalen.se/Sighting/135851807</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135574610</v>
+        <v>135851811</v>
       </c>
       <c r="B59" t="n">
-        <v>57980</v>
+        <v>99298</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442382</v>
+        <v>442432</v>
       </c>
       <c r="R59" t="n">
-        <v>7027768</v>
+        <v>7027742</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7352,27 +7214,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7387,49 +7244,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574610</t>
+          <t>https://artportalen.se/Sighting/135851811</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574611</v>
+        <v>135574569</v>
       </c>
       <c r="B60" t="n">
-        <v>57980</v>
+        <v>99303</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>222118</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7439,10 +7296,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442414</v>
+        <v>442283</v>
       </c>
       <c r="R60" t="n">
-        <v>7027804</v>
+        <v>7027534</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7474,7 +7331,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7484,12 +7341,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7515,59 +7367,54 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574611</t>
+          <t>https://artportalen.se/Sighting/135574569</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135574612</v>
+        <v>135851787</v>
       </c>
       <c r="B61" t="n">
-        <v>57980</v>
+        <v>104795</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442425</v>
+        <v>442360</v>
       </c>
       <c r="R61" t="n">
-        <v>7027761</v>
+        <v>7027578</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7591,27 +7438,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7626,70 +7468,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574612</t>
+          <t>https://artportalen.se/Sighting/135851787</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135574616</v>
+        <v>135851801</v>
       </c>
       <c r="B62" t="n">
-        <v>57980</v>
+        <v>104795</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442455</v>
+        <v>442243</v>
       </c>
       <c r="R62" t="n">
-        <v>7027671</v>
+        <v>7027546</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7713,27 +7550,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7748,70 +7580,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574616</t>
+          <t>https://artportalen.se/Sighting/135851801</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135574617</v>
+        <v>135851775</v>
       </c>
       <c r="B63" t="n">
-        <v>57980</v>
+        <v>100301</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442432</v>
+        <v>442475</v>
       </c>
       <c r="R63" t="n">
-        <v>7027650</v>
+        <v>7027687</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,27 +7662,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7870,70 +7692,74 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574617</t>
+          <t>https://artportalen.se/Sighting/135851775</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135574625</v>
+        <v>55633849</v>
       </c>
       <c r="B64" t="n">
-        <v>57980</v>
+        <v>101326</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442465</v>
+        <v>442283</v>
       </c>
       <c r="R64" t="n">
-        <v>7027665</v>
+        <v>7027836</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7957,27 +7783,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7988,53 +7804,58 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574625</t>
+          <t>https://artportalen.se/Sighting/55633849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574626</v>
+        <v>135574547</v>
       </c>
       <c r="B65" t="n">
-        <v>57980</v>
+        <v>101485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8044,10 +7865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442550</v>
+        <v>442418</v>
       </c>
       <c r="R65" t="n">
-        <v>7027681</v>
+        <v>7027847</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8079,7 +7900,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8089,12 +7910,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8120,54 +7936,58 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574626</t>
+          <t>https://artportalen.se/Sighting/135574547</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135574627</v>
+        <v>5168927</v>
       </c>
       <c r="B66" t="n">
-        <v>57980</v>
+        <v>98137</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442492</v>
+        <v>442283</v>
       </c>
       <c r="R66" t="n">
-        <v>7027713</v>
+        <v>7027836</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8191,27 +8011,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8222,74 +8032,82 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574627</t>
+          <t>https://artportalen.se/Sighting/5168927</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135574628</v>
+        <v>135851788</v>
       </c>
       <c r="B67" t="n">
-        <v>57980</v>
+        <v>101375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442502</v>
+        <v>442339</v>
       </c>
       <c r="R67" t="n">
-        <v>7027719</v>
+        <v>7027583</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8313,27 +8131,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8342,68 +8155,77 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574628</t>
+          <t>https://artportalen.se/Sighting/135851788</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851785</v>
+        <v>135851791</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>101375</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442360</v>
+        <v>442312</v>
       </c>
       <c r="R68" t="n">
-        <v>7027581</v>
+        <v>7027596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8435,7 +8257,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8445,7 +8267,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,6 +8276,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8470,3451 +8293,6 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135851790</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>442323</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135851813</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>442444</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7027735</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135635857</v>
-      </c>
-      <c r="B71" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>442366</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2596274</v>
-      </c>
-      <c r="B72" t="n">
-        <v>99017</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>219795</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Grönkulla</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135574548</v>
-      </c>
-      <c r="B73" t="n">
-        <v>99278</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7027839</v>
-      </c>
-      <c r="S73" t="n">
-        <v>3</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135574614</v>
-      </c>
-      <c r="B74" t="n">
-        <v>99278</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>442464</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7027693</v>
-      </c>
-      <c r="S74" t="n">
-        <v>3</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135851773</v>
-      </c>
-      <c r="B75" t="n">
-        <v>99278</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>442469</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7027704</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135851816</v>
-      </c>
-      <c r="B76" t="n">
-        <v>99278</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7027780</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135574549</v>
-      </c>
-      <c r="B77" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135851772</v>
-      </c>
-      <c r="B78" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7027706</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135851793</v>
-      </c>
-      <c r="B79" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>442287</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135851800</v>
-      </c>
-      <c r="B80" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>442247</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135851804</v>
-      </c>
-      <c r="B81" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135851814</v>
-      </c>
-      <c r="B82" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>442453</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7027747</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135851815</v>
-      </c>
-      <c r="B83" t="n">
-        <v>99300</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>442471</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7027763</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135851774</v>
-      </c>
-      <c r="B84" t="n">
-        <v>108364</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>220102</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Kärrfibbla</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Crepis paludosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>442467</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7027703</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>4041960</v>
-      </c>
-      <c r="B85" t="n">
-        <v>106229</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135851789</v>
-      </c>
-      <c r="B86" t="n">
-        <v>106398</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>442341</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7027597</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135851806</v>
-      </c>
-      <c r="B87" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>442315</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7027602</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135851807</v>
-      </c>
-      <c r="B88" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>442368</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135851811</v>
-      </c>
-      <c r="B89" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>442432</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7027742</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135574569</v>
-      </c>
-      <c r="B90" t="n">
-        <v>99303</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>222118</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Flugblomster</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Ophrys insectifera</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7027534</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135851787</v>
-      </c>
-      <c r="B91" t="n">
-        <v>104795</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>442360</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7027578</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135851801</v>
-      </c>
-      <c r="B92" t="n">
-        <v>104795</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>442243</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135851775</v>
-      </c>
-      <c r="B93" t="n">
-        <v>100301</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>222467</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gräsull</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>442475</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7027687</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>55633849</v>
-      </c>
-      <c r="B94" t="n">
-        <v>101326</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135574547</v>
-      </c>
-      <c r="B95" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>442418</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7027847</v>
-      </c>
-      <c r="S95" t="n">
-        <v>3</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5168927</v>
-      </c>
-      <c r="B96" t="n">
-        <v>98137</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>222741</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Finbräken</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Cystopteris montana</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135851788</v>
-      </c>
-      <c r="B97" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>442339</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7027583</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>135851791</v>
-      </c>
-      <c r="B98" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>442312</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -11989,36 +8367,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574556</v>
+        <v>135574538</v>
       </c>
       <c r="B37" t="n">
         <v>57980</v>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442329</v>
+        <v>442449</v>
       </c>
       <c r="R37" t="n">
-        <v>7027573</v>
+        <v>7027722</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135574538</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135851785</v>
+        <v>135574539</v>
       </c>
       <c r="B38" t="n">
         <v>57980</v>
@@ -4772,19 +4772,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442360</v>
+        <v>442445</v>
       </c>
       <c r="R38" t="n">
-        <v>7027581</v>
+        <v>7027731</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4808,22 +4813,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,24 +4848,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
+          <t>https://artportalen.se/Sighting/135574539</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135851790</v>
+        <v>135574540</v>
       </c>
       <c r="B39" t="n">
         <v>57980</v>
@@ -4884,27 +4894,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442323</v>
+        <v>442421</v>
       </c>
       <c r="R39" t="n">
-        <v>7027596</v>
+        <v>7027753</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4928,27 +4935,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,24 +4970,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
+          <t>https://artportalen.se/Sighting/135574540</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135851813</v>
+        <v>135574541</v>
       </c>
       <c r="B40" t="n">
         <v>57980</v>
@@ -5009,27 +5016,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442444</v>
+        <v>442414</v>
       </c>
       <c r="R40" t="n">
-        <v>7027735</v>
+        <v>7027802</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5053,27 +5057,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,27 +5092,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
+          <t>https://artportalen.se/Sighting/135574541</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135635857</v>
+        <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,34 +5120,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5152,13 +5149,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442366</v>
+        <v>442437</v>
       </c>
       <c r="R41" t="n">
-        <v>7027641</v>
+        <v>7027801</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5185,9 +5182,24 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,58 +5225,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
+          <t>https://artportalen.se/Sighting/135574542</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2596274</v>
+        <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>99017</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442283</v>
+        <v>442430</v>
       </c>
       <c r="R42" t="n">
-        <v>7027836</v>
+        <v>7027816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5288,17 +5301,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,74 +5332,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
+          <t>https://artportalen.se/Sighting/135574544</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574548</v>
+        <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>99278</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442411</v>
+        <v>442350</v>
       </c>
       <c r="R43" t="n">
-        <v>7027839</v>
+        <v>7027791</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,7 +5428,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5415,7 +5438,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,38 +5469,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
+          <t>https://artportalen.se/Sighting/135574550</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574614</v>
+        <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>99278</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5482,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442464</v>
+        <v>442295</v>
       </c>
       <c r="R44" t="n">
-        <v>7027693</v>
+        <v>7027775</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5517,7 +5545,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5527,7 +5555,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5553,62 +5586,58 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
+          <t>https://artportalen.se/Sighting/135574551</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135851773</v>
+        <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>99278</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442469</v>
+        <v>442327</v>
       </c>
       <c r="R45" t="n">
-        <v>7027704</v>
+        <v>7027590</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5632,22 +5661,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5656,72 +5690,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
+          <t>https://artportalen.se/Sighting/135574553</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135851816</v>
+        <v>135574556</v>
       </c>
       <c r="B46" t="n">
-        <v>99278</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442473</v>
+        <v>442329</v>
       </c>
       <c r="R46" t="n">
-        <v>7027780</v>
+        <v>7027573</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5745,29 +5783,34 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5775,62 +5818,67 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574549</v>
+        <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442411</v>
+        <v>442329</v>
       </c>
       <c r="R47" t="n">
-        <v>7027836</v>
+        <v>7027569</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5862,7 +5910,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5872,7 +5920,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5898,62 +5951,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
+          <t>https://artportalen.se/Sighting/135574558</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135851772</v>
+        <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442473</v>
+        <v>442311</v>
       </c>
       <c r="R48" t="n">
-        <v>7027706</v>
+        <v>7027581</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5977,22 +6027,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,72 +6056,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
+          <t>https://artportalen.se/Sighting/135574560</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135851793</v>
+        <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442287</v>
+        <v>442291</v>
       </c>
       <c r="R49" t="n">
-        <v>7027599</v>
+        <v>7027577</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6090,22 +6149,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6120,65 +6184,70 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
+          <t>https://artportalen.se/Sighting/135574561</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135851800</v>
+        <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442247</v>
+        <v>442296</v>
       </c>
       <c r="R50" t="n">
-        <v>7027546</v>
+        <v>7027551</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6271,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,65 +6306,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
+          <t>https://artportalen.se/Sighting/135574575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135851804</v>
+        <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442275</v>
+        <v>442295</v>
       </c>
       <c r="R51" t="n">
-        <v>7027599</v>
+        <v>7027519</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6314,22 +6392,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6344,65 +6427,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
+          <t>https://artportalen.se/Sighting/135574580</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135851814</v>
+        <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442453</v>
+        <v>442348</v>
       </c>
       <c r="R52" t="n">
-        <v>7027747</v>
+        <v>7027560</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6426,22 +6513,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6456,65 +6548,70 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
+          <t>https://artportalen.se/Sighting/135574585</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135851815</v>
+        <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442471</v>
+        <v>442355</v>
       </c>
       <c r="R53" t="n">
-        <v>7027763</v>
+        <v>7027577</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,22 +6635,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6568,65 +6670,70 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
+          <t>https://artportalen.se/Sighting/135574587</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135851774</v>
+        <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>108364</v>
+        <v>57980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442467</v>
+        <v>442386</v>
       </c>
       <c r="R54" t="n">
-        <v>7027703</v>
+        <v>7027567</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6650,22 +6757,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6680,69 +6792,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
+          <t>https://artportalen.se/Sighting/135574590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4041960</v>
+        <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>106229</v>
+        <v>57980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442283</v>
+        <v>442362</v>
       </c>
       <c r="R55" t="n">
-        <v>7027836</v>
+        <v>7027657</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6766,17 +6874,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6787,74 +6905,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
+          <t>https://artportalen.se/Sighting/135574593</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135851789</v>
+        <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>106398</v>
+        <v>57980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442341</v>
+        <v>442387</v>
       </c>
       <c r="R56" t="n">
-        <v>7027597</v>
+        <v>7027641</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6878,22 +6996,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6908,65 +7031,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
+          <t>https://artportalen.se/Sighting/135574601</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135851806</v>
+        <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>99298</v>
+        <v>57980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442315</v>
+        <v>442416</v>
       </c>
       <c r="R57" t="n">
-        <v>7027602</v>
+        <v>7027567</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6990,22 +7113,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7020,65 +7148,70 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
+          <t>https://artportalen.se/Sighting/135574605</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135851807</v>
+        <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>99298</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442368</v>
+        <v>442410</v>
       </c>
       <c r="R58" t="n">
-        <v>7027641</v>
+        <v>7027707</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7102,22 +7235,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7132,65 +7270,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
+          <t>https://artportalen.se/Sighting/135574608</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135851811</v>
+        <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>99298</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442432</v>
+        <v>442382</v>
       </c>
       <c r="R59" t="n">
-        <v>7027742</v>
+        <v>7027768</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,22 +7352,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,49 +7387,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
+          <t>https://artportalen.se/Sighting/135574610</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574569</v>
+        <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>99303</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222118</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7296,10 +7439,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442283</v>
+        <v>442414</v>
       </c>
       <c r="R60" t="n">
-        <v>7027534</v>
+        <v>7027804</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7331,7 +7474,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7341,7 +7484,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7367,54 +7515,59 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
+          <t>https://artportalen.se/Sighting/135574611</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135851787</v>
+        <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>104795</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442360</v>
+        <v>442425</v>
       </c>
       <c r="R61" t="n">
-        <v>7027578</v>
+        <v>7027761</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,22 +7591,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,65 +7626,70 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
+          <t>https://artportalen.se/Sighting/135574612</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135851801</v>
+        <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>104795</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442243</v>
+        <v>442455</v>
       </c>
       <c r="R62" t="n">
-        <v>7027546</v>
+        <v>7027671</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7550,22 +7713,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7580,65 +7748,70 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
+          <t>https://artportalen.se/Sighting/135574616</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135851775</v>
+        <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>100301</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222467</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442475</v>
+        <v>442432</v>
       </c>
       <c r="R63" t="n">
-        <v>7027687</v>
+        <v>7027650</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7662,22 +7835,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,74 +7870,70 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
+          <t>https://artportalen.se/Sighting/135574617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>55633849</v>
+        <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>101326</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442283</v>
+        <v>442465</v>
       </c>
       <c r="R64" t="n">
-        <v>7027836</v>
+        <v>7027665</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7783,17 +7957,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7804,58 +7988,53 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
+          <t>https://artportalen.se/Sighting/135574625</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574547</v>
+        <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>101485</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7865,10 +8044,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442418</v>
+        <v>442550</v>
       </c>
       <c r="R65" t="n">
-        <v>7027847</v>
+        <v>7027681</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7900,7 +8079,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7910,7 +8089,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7936,58 +8120,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
+          <t>https://artportalen.se/Sighting/135574626</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5168927</v>
+        <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>98137</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442283</v>
+        <v>442492</v>
       </c>
       <c r="R66" t="n">
-        <v>7027836</v>
+        <v>7027713</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8011,17 +8191,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8032,82 +8222,74 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
+          <t>https://artportalen.se/Sighting/135574627</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135851788</v>
+        <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>101375</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442339</v>
+        <v>442502</v>
       </c>
       <c r="R67" t="n">
-        <v>7027583</v>
+        <v>7027719</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8131,22 +8313,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8155,77 +8342,68 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
+          <t>https://artportalen.se/Sighting/135574628</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851791</v>
+        <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>101375</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442312</v>
+        <v>442360</v>
       </c>
       <c r="R68" t="n">
-        <v>7027596</v>
+        <v>7027581</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8257,7 +8435,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8267,7 +8445,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8276,7 +8454,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8293,6 +8470,3451 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851785</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135851790</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>442323</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851790</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135851813</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>442444</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7027735</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851813</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135635857</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>442366</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135635857</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2596274</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2596274</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135574548</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99278</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7027839</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574548</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135574614</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99278</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>442464</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7027693</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574614</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135851773</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99278</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>442469</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7027704</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851773</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135851816</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99278</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7027780</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851816</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135574549</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574549</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135851772</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7027706</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851772</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135851793</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>442287</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851793</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135851800</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>442247</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851800</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135851804</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851804</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135851814</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>442453</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7027747</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851814</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135851815</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>442471</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7027763</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851815</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135851774</v>
+      </c>
+      <c r="B84" t="n">
+        <v>108364</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>442467</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7027703</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851774</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4041960</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4041960</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135851789</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106398</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>442341</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7027597</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851789</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135851806</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>442315</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7027602</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851806</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135851807</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>442368</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851807</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135851811</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>442432</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7027742</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851811</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135574569</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99303</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7027534</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574569</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135851787</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104795</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>442360</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7027578</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851787</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135851801</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104795</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>442243</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851801</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135851775</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100301</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>442475</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7027687</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851775</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>55633849</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55633849</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135574547</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>442418</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7027847</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574547</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5168927</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5168927</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135851788</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>442339</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7027583</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851788</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135851791</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>442312</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -8367,6 +11989,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135574586</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135574589</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135574591</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135574594</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135574597</v>
       </c>
       <c r="B10" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135574609</v>
       </c>
       <c r="B11" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135574620</v>
       </c>
       <c r="B12" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135574581</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135574623</v>
       </c>
       <c r="B14" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135574565</v>
       </c>
       <c r="B16" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96491</v>
+        <v>96508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96491</v>
+        <v>96508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135574562</v>
       </c>
       <c r="B23" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91582</v>
+        <v>91584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>135574545</v>
       </c>
       <c r="B25" t="n">
-        <v>93383</v>
+        <v>93398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93383</v>
+        <v>93398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93383</v>
+        <v>93398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93383</v>
+        <v>93398</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135574538</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>135574539</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>135574540</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135574541</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>135574556</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>135851790</v>
       </c>
       <c r="B69" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>135851813</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>135635857</v>
       </c>
       <c r="B71" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135574548</v>
       </c>
       <c r="B73" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135574614</v>
       </c>
       <c r="B74" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>135574549</v>
       </c>
       <c r="B77" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>135574569</v>
       </c>
       <c r="B90" t="n">
-        <v>99303</v>
+        <v>99320</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100301</v>
+        <v>100318</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135574547</v>
       </c>
       <c r="B95" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574538</v>
+        <v>135574556</v>
       </c>
       <c r="B37" t="n">
         <v>57982</v>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442449</v>
+        <v>442329</v>
       </c>
       <c r="R37" t="n">
-        <v>7027722</v>
+        <v>7027573</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574538</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574539</v>
+        <v>135851785</v>
       </c>
       <c r="B38" t="n">
         <v>57982</v>
@@ -4772,24 +4772,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442445</v>
+        <v>442360</v>
       </c>
       <c r="R38" t="n">
-        <v>7027731</v>
+        <v>7027581</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4813,27 +4808,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,24 +4838,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574539</t>
+          <t>https://artportalen.se/Sighting/135851785</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574540</v>
+        <v>135851790</v>
       </c>
       <c r="B39" t="n">
         <v>57982</v>
@@ -4894,24 +4884,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442421</v>
+        <v>442323</v>
       </c>
       <c r="R39" t="n">
-        <v>7027753</v>
+        <v>7027596</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4935,27 +4928,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4970,24 +4963,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574540</t>
+          <t>https://artportalen.se/Sighting/135851790</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574541</v>
+        <v>135851813</v>
       </c>
       <c r="B40" t="n">
         <v>57982</v>
@@ -5016,24 +5009,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442414</v>
+        <v>442444</v>
       </c>
       <c r="R40" t="n">
-        <v>7027802</v>
+        <v>7027735</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5057,27 +5053,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,27 +5088,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574541</t>
+          <t>https://artportalen.se/Sighting/135851813</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574542</v>
+        <v>135635857</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5120,27 +5116,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5149,13 +5152,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442437</v>
+        <v>442366</v>
       </c>
       <c r="R41" t="n">
-        <v>7027801</v>
+        <v>7027641</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,24 +5185,9 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5225,59 +5213,58 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574542</t>
+          <t>https://artportalen.se/Sighting/135635857</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574544</v>
+        <v>2596274</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>99017</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442430</v>
+        <v>442283</v>
       </c>
       <c r="R42" t="n">
-        <v>7027816</v>
+        <v>7027836</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5301,27 +5288,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5332,74 +5309,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574544</t>
+          <t>https://artportalen.se/Sighting/2596274</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574550</v>
+        <v>135574548</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442350</v>
+        <v>442411</v>
       </c>
       <c r="R43" t="n">
-        <v>7027791</v>
+        <v>7027839</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5428,7 +5405,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5438,12 +5415,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,38 +5441,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574550</t>
+          <t>https://artportalen.se/Sighting/135574548</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574551</v>
+        <v>135574614</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5510,10 +5482,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442295</v>
+        <v>442464</v>
       </c>
       <c r="R44" t="n">
-        <v>7027775</v>
+        <v>7027693</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5545,7 +5517,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5555,12 +5527,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5586,58 +5553,62 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574551</t>
+          <t>https://artportalen.se/Sighting/135574614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574553</v>
+        <v>135851773</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442327</v>
+        <v>442469</v>
       </c>
       <c r="R45" t="n">
-        <v>7027590</v>
+        <v>7027704</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5661,27 +5632,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,76 +5656,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574553</t>
+          <t>https://artportalen.se/Sighting/135851773</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574556</v>
+        <v>135851816</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442329</v>
+        <v>442473</v>
       </c>
       <c r="R46" t="n">
-        <v>7027573</v>
+        <v>7027780</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5783,34 +5745,29 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5818,67 +5775,62 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135851816</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574558</v>
+        <v>135574549</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442329</v>
+        <v>442411</v>
       </c>
       <c r="R47" t="n">
-        <v>7027569</v>
+        <v>7027836</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5910,7 +5862,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5920,12 +5872,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5951,59 +5898,62 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574558</t>
+          <t>https://artportalen.se/Sighting/135574549</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574560</v>
+        <v>135851772</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442311</v>
+        <v>442473</v>
       </c>
       <c r="R48" t="n">
-        <v>7027581</v>
+        <v>7027706</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6027,27 +5977,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6056,76 +6001,72 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574560</t>
+          <t>https://artportalen.se/Sighting/135851772</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574561</v>
+        <v>135851793</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442291</v>
+        <v>442287</v>
       </c>
       <c r="R49" t="n">
-        <v>7027577</v>
+        <v>7027599</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,27 +6090,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6184,70 +6120,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574561</t>
+          <t>https://artportalen.se/Sighting/135851793</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574575</v>
+        <v>135851800</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442296</v>
+        <v>442247</v>
       </c>
       <c r="R50" t="n">
-        <v>7027551</v>
+        <v>7027546</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,27 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6306,69 +6232,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574575</t>
+          <t>https://artportalen.se/Sighting/135851800</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574580</v>
+        <v>135851804</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442295</v>
+        <v>442275</v>
       </c>
       <c r="R51" t="n">
-        <v>7027519</v>
+        <v>7027599</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6392,27 +6314,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,69 +6344,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574580</t>
+          <t>https://artportalen.se/Sighting/135851804</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574585</v>
+        <v>135851814</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442348</v>
+        <v>442453</v>
       </c>
       <c r="R52" t="n">
-        <v>7027560</v>
+        <v>7027747</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6513,27 +6426,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,70 +6456,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574585</t>
+          <t>https://artportalen.se/Sighting/135851814</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574587</v>
+        <v>135851815</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442355</v>
+        <v>442471</v>
       </c>
       <c r="R53" t="n">
-        <v>7027577</v>
+        <v>7027763</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6635,27 +6538,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6670,70 +6568,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574587</t>
+          <t>https://artportalen.se/Sighting/135851815</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574590</v>
+        <v>135851774</v>
       </c>
       <c r="B54" t="n">
-        <v>57982</v>
+        <v>108387</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442386</v>
+        <v>442467</v>
       </c>
       <c r="R54" t="n">
-        <v>7027567</v>
+        <v>7027703</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6757,27 +6650,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6792,65 +6680,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574590</t>
+          <t>https://artportalen.se/Sighting/135851774</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574593</v>
+        <v>4041960</v>
       </c>
       <c r="B55" t="n">
-        <v>57982</v>
+        <v>106229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442362</v>
+        <v>442283</v>
       </c>
       <c r="R55" t="n">
-        <v>7027657</v>
+        <v>7027836</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6874,27 +6766,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6905,74 +6787,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574593</t>
+          <t>https://artportalen.se/Sighting/4041960</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135574601</v>
+        <v>135851789</v>
       </c>
       <c r="B56" t="n">
-        <v>57982</v>
+        <v>106418</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442387</v>
+        <v>442341</v>
       </c>
       <c r="R56" t="n">
-        <v>7027641</v>
+        <v>7027597</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,27 +6878,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7031,65 +6908,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574601</t>
+          <t>https://artportalen.se/Sighting/135851789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135574605</v>
+        <v>135851806</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>99315</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442416</v>
+        <v>442315</v>
       </c>
       <c r="R57" t="n">
-        <v>7027567</v>
+        <v>7027602</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,27 +6990,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7148,70 +7020,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574605</t>
+          <t>https://artportalen.se/Sighting/135851806</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135574608</v>
+        <v>135851807</v>
       </c>
       <c r="B58" t="n">
-        <v>57982</v>
+        <v>99315</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442410</v>
+        <v>442368</v>
       </c>
       <c r="R58" t="n">
-        <v>7027707</v>
+        <v>7027641</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7235,27 +7102,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7270,65 +7132,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574608</t>
+          <t>https://artportalen.se/Sighting/135851807</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135574610</v>
+        <v>135851811</v>
       </c>
       <c r="B59" t="n">
-        <v>57982</v>
+        <v>99315</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442382</v>
+        <v>442432</v>
       </c>
       <c r="R59" t="n">
-        <v>7027768</v>
+        <v>7027742</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7352,27 +7214,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7387,49 +7244,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574610</t>
+          <t>https://artportalen.se/Sighting/135851811</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574611</v>
+        <v>135574569</v>
       </c>
       <c r="B60" t="n">
-        <v>57982</v>
+        <v>99320</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>222118</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7439,10 +7296,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442414</v>
+        <v>442283</v>
       </c>
       <c r="R60" t="n">
-        <v>7027804</v>
+        <v>7027534</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7474,7 +7331,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7484,12 +7341,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7515,59 +7367,54 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574611</t>
+          <t>https://artportalen.se/Sighting/135574569</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135574612</v>
+        <v>135851787</v>
       </c>
       <c r="B61" t="n">
-        <v>57982</v>
+        <v>104815</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442425</v>
+        <v>442360</v>
       </c>
       <c r="R61" t="n">
-        <v>7027761</v>
+        <v>7027578</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7591,27 +7438,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7626,70 +7468,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574612</t>
+          <t>https://artportalen.se/Sighting/135851787</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135574616</v>
+        <v>135851801</v>
       </c>
       <c r="B62" t="n">
-        <v>57982</v>
+        <v>104815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442455</v>
+        <v>442243</v>
       </c>
       <c r="R62" t="n">
-        <v>7027671</v>
+        <v>7027546</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7713,27 +7550,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7748,70 +7580,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574616</t>
+          <t>https://artportalen.se/Sighting/135851801</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135574617</v>
+        <v>135851775</v>
       </c>
       <c r="B63" t="n">
-        <v>57982</v>
+        <v>100318</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442432</v>
+        <v>442475</v>
       </c>
       <c r="R63" t="n">
-        <v>7027650</v>
+        <v>7027687</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,27 +7662,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7870,70 +7692,74 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574617</t>
+          <t>https://artportalen.se/Sighting/135851775</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135574625</v>
+        <v>55633849</v>
       </c>
       <c r="B64" t="n">
-        <v>57982</v>
+        <v>101326</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442465</v>
+        <v>442283</v>
       </c>
       <c r="R64" t="n">
-        <v>7027665</v>
+        <v>7027836</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7957,27 +7783,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7988,53 +7804,58 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574625</t>
+          <t>https://artportalen.se/Sighting/55633849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574626</v>
+        <v>135574547</v>
       </c>
       <c r="B65" t="n">
-        <v>57982</v>
+        <v>101502</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8044,10 +7865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442550</v>
+        <v>442418</v>
       </c>
       <c r="R65" t="n">
-        <v>7027681</v>
+        <v>7027847</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8079,7 +7900,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8089,12 +7910,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8120,54 +7936,58 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574626</t>
+          <t>https://artportalen.se/Sighting/135574547</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135574627</v>
+        <v>5168927</v>
       </c>
       <c r="B66" t="n">
-        <v>57982</v>
+        <v>98137</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442492</v>
+        <v>442283</v>
       </c>
       <c r="R66" t="n">
-        <v>7027713</v>
+        <v>7027836</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8191,27 +8011,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8222,74 +8032,82 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574627</t>
+          <t>https://artportalen.se/Sighting/5168927</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135574628</v>
+        <v>135851788</v>
       </c>
       <c r="B67" t="n">
-        <v>57982</v>
+        <v>101392</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442502</v>
+        <v>442339</v>
       </c>
       <c r="R67" t="n">
-        <v>7027719</v>
+        <v>7027583</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8313,27 +8131,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8342,68 +8155,77 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574628</t>
+          <t>https://artportalen.se/Sighting/135851788</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851785</v>
+        <v>135851791</v>
       </c>
       <c r="B68" t="n">
-        <v>57982</v>
+        <v>101392</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442360</v>
+        <v>442312</v>
       </c>
       <c r="R68" t="n">
-        <v>7027581</v>
+        <v>7027596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8435,7 +8257,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8445,7 +8267,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,6 +8276,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8470,3451 +8293,6 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135851790</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>442323</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135851813</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>442444</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7027735</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135635857</v>
-      </c>
-      <c r="B71" t="n">
-        <v>58143</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>442366</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2596274</v>
-      </c>
-      <c r="B72" t="n">
-        <v>99017</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>219795</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Grönkulla</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135574548</v>
-      </c>
-      <c r="B73" t="n">
-        <v>99295</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7027839</v>
-      </c>
-      <c r="S73" t="n">
-        <v>3</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135574614</v>
-      </c>
-      <c r="B74" t="n">
-        <v>99295</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>442464</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7027693</v>
-      </c>
-      <c r="S74" t="n">
-        <v>3</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135851773</v>
-      </c>
-      <c r="B75" t="n">
-        <v>99295</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>442469</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7027704</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135851816</v>
-      </c>
-      <c r="B76" t="n">
-        <v>99295</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7027780</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135574549</v>
-      </c>
-      <c r="B77" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135851772</v>
-      </c>
-      <c r="B78" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7027706</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135851793</v>
-      </c>
-      <c r="B79" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>442287</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135851800</v>
-      </c>
-      <c r="B80" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>442247</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135851804</v>
-      </c>
-      <c r="B81" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135851814</v>
-      </c>
-      <c r="B82" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>442453</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7027747</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135851815</v>
-      </c>
-      <c r="B83" t="n">
-        <v>99317</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>442471</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7027763</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135851774</v>
-      </c>
-      <c r="B84" t="n">
-        <v>108387</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>220102</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Kärrfibbla</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Crepis paludosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>442467</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7027703</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>4041960</v>
-      </c>
-      <c r="B85" t="n">
-        <v>106229</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135851789</v>
-      </c>
-      <c r="B86" t="n">
-        <v>106418</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>442341</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7027597</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135851806</v>
-      </c>
-      <c r="B87" t="n">
-        <v>99315</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>442315</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7027602</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135851807</v>
-      </c>
-      <c r="B88" t="n">
-        <v>99315</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>442368</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135851811</v>
-      </c>
-      <c r="B89" t="n">
-        <v>99315</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>442432</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7027742</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135574569</v>
-      </c>
-      <c r="B90" t="n">
-        <v>99320</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>222118</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Flugblomster</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Ophrys insectifera</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7027534</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135851787</v>
-      </c>
-      <c r="B91" t="n">
-        <v>104815</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>442360</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7027578</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135851801</v>
-      </c>
-      <c r="B92" t="n">
-        <v>104815</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>442243</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135851775</v>
-      </c>
-      <c r="B93" t="n">
-        <v>100318</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>222467</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gräsull</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>442475</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7027687</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>55633849</v>
-      </c>
-      <c r="B94" t="n">
-        <v>101326</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135574547</v>
-      </c>
-      <c r="B95" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>442418</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7027847</v>
-      </c>
-      <c r="S95" t="n">
-        <v>3</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5168927</v>
-      </c>
-      <c r="B96" t="n">
-        <v>98137</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>222741</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Finbräken</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Cystopteris montana</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135851788</v>
-      </c>
-      <c r="B97" t="n">
-        <v>101392</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>442339</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7027583</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>135851791</v>
-      </c>
-      <c r="B98" t="n">
-        <v>101392</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>442312</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -11989,36 +8367,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574556</v>
+        <v>135574538</v>
       </c>
       <c r="B37" t="n">
         <v>57982</v>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442329</v>
+        <v>442449</v>
       </c>
       <c r="R37" t="n">
-        <v>7027573</v>
+        <v>7027722</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135574538</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135851785</v>
+        <v>135574539</v>
       </c>
       <c r="B38" t="n">
         <v>57982</v>
@@ -4772,19 +4772,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442360</v>
+        <v>442445</v>
       </c>
       <c r="R38" t="n">
-        <v>7027581</v>
+        <v>7027731</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4808,22 +4813,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,24 +4848,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
+          <t>https://artportalen.se/Sighting/135574539</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135851790</v>
+        <v>135574540</v>
       </c>
       <c r="B39" t="n">
         <v>57982</v>
@@ -4884,27 +4894,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442323</v>
+        <v>442421</v>
       </c>
       <c r="R39" t="n">
-        <v>7027596</v>
+        <v>7027753</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4928,27 +4935,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,24 +4970,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
+          <t>https://artportalen.se/Sighting/135574540</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135851813</v>
+        <v>135574541</v>
       </c>
       <c r="B40" t="n">
         <v>57982</v>
@@ -5009,27 +5016,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442444</v>
+        <v>442414</v>
       </c>
       <c r="R40" t="n">
-        <v>7027735</v>
+        <v>7027802</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5053,27 +5057,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,27 +5092,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
+          <t>https://artportalen.se/Sighting/135574541</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135635857</v>
+        <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,34 +5120,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5152,13 +5149,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442366</v>
+        <v>442437</v>
       </c>
       <c r="R41" t="n">
-        <v>7027641</v>
+        <v>7027801</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5185,9 +5182,24 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,58 +5225,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
+          <t>https://artportalen.se/Sighting/135574542</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2596274</v>
+        <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>99017</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442283</v>
+        <v>442430</v>
       </c>
       <c r="R42" t="n">
-        <v>7027836</v>
+        <v>7027816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5288,17 +5301,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,74 +5332,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
+          <t>https://artportalen.se/Sighting/135574544</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574548</v>
+        <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442411</v>
+        <v>442350</v>
       </c>
       <c r="R43" t="n">
-        <v>7027839</v>
+        <v>7027791</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,7 +5428,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5415,7 +5438,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,38 +5469,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
+          <t>https://artportalen.se/Sighting/135574550</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574614</v>
+        <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5482,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442464</v>
+        <v>442295</v>
       </c>
       <c r="R44" t="n">
-        <v>7027693</v>
+        <v>7027775</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5517,7 +5545,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5527,7 +5555,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5553,62 +5586,58 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
+          <t>https://artportalen.se/Sighting/135574551</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135851773</v>
+        <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442469</v>
+        <v>442327</v>
       </c>
       <c r="R45" t="n">
-        <v>7027704</v>
+        <v>7027590</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5632,22 +5661,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5656,72 +5690,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
+          <t>https://artportalen.se/Sighting/135574553</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135851816</v>
+        <v>135574556</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442473</v>
+        <v>442329</v>
       </c>
       <c r="R46" t="n">
-        <v>7027780</v>
+        <v>7027573</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5745,29 +5783,34 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5775,62 +5818,67 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574549</v>
+        <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442411</v>
+        <v>442329</v>
       </c>
       <c r="R47" t="n">
-        <v>7027836</v>
+        <v>7027569</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5862,7 +5910,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5872,7 +5920,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5898,62 +5951,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
+          <t>https://artportalen.se/Sighting/135574558</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135851772</v>
+        <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442473</v>
+        <v>442311</v>
       </c>
       <c r="R48" t="n">
-        <v>7027706</v>
+        <v>7027581</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5977,22 +6027,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,72 +6056,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
+          <t>https://artportalen.se/Sighting/135574560</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135851793</v>
+        <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442287</v>
+        <v>442291</v>
       </c>
       <c r="R49" t="n">
-        <v>7027599</v>
+        <v>7027577</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6090,22 +6149,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6120,65 +6184,70 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
+          <t>https://artportalen.se/Sighting/135574561</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135851800</v>
+        <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442247</v>
+        <v>442296</v>
       </c>
       <c r="R50" t="n">
-        <v>7027546</v>
+        <v>7027551</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6271,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,65 +6306,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
+          <t>https://artportalen.se/Sighting/135574575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135851804</v>
+        <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442275</v>
+        <v>442295</v>
       </c>
       <c r="R51" t="n">
-        <v>7027599</v>
+        <v>7027519</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6314,22 +6392,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6344,65 +6427,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
+          <t>https://artportalen.se/Sighting/135574580</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135851814</v>
+        <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442453</v>
+        <v>442348</v>
       </c>
       <c r="R52" t="n">
-        <v>7027747</v>
+        <v>7027560</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6426,22 +6513,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6456,65 +6548,70 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
+          <t>https://artportalen.se/Sighting/135574585</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135851815</v>
+        <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442471</v>
+        <v>442355</v>
       </c>
       <c r="R53" t="n">
-        <v>7027763</v>
+        <v>7027577</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,22 +6635,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6568,65 +6670,70 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
+          <t>https://artportalen.se/Sighting/135574587</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135851774</v>
+        <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>108387</v>
+        <v>57982</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442467</v>
+        <v>442386</v>
       </c>
       <c r="R54" t="n">
-        <v>7027703</v>
+        <v>7027567</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6650,22 +6757,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6680,69 +6792,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
+          <t>https://artportalen.se/Sighting/135574590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4041960</v>
+        <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>106229</v>
+        <v>57982</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442283</v>
+        <v>442362</v>
       </c>
       <c r="R55" t="n">
-        <v>7027836</v>
+        <v>7027657</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6766,17 +6874,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6787,74 +6905,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
+          <t>https://artportalen.se/Sighting/135574593</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135851789</v>
+        <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>106418</v>
+        <v>57982</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442341</v>
+        <v>442387</v>
       </c>
       <c r="R56" t="n">
-        <v>7027597</v>
+        <v>7027641</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6878,22 +6996,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6908,65 +7031,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
+          <t>https://artportalen.se/Sighting/135574601</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135851806</v>
+        <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>99315</v>
+        <v>57982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442315</v>
+        <v>442416</v>
       </c>
       <c r="R57" t="n">
-        <v>7027602</v>
+        <v>7027567</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6990,22 +7113,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7020,65 +7148,70 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
+          <t>https://artportalen.se/Sighting/135574605</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135851807</v>
+        <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>99315</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442368</v>
+        <v>442410</v>
       </c>
       <c r="R58" t="n">
-        <v>7027641</v>
+        <v>7027707</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7102,22 +7235,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7132,65 +7270,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
+          <t>https://artportalen.se/Sighting/135574608</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135851811</v>
+        <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>99315</v>
+        <v>57982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442432</v>
+        <v>442382</v>
       </c>
       <c r="R59" t="n">
-        <v>7027742</v>
+        <v>7027768</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,22 +7352,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,49 +7387,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
+          <t>https://artportalen.se/Sighting/135574610</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574569</v>
+        <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>99320</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222118</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7296,10 +7439,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442283</v>
+        <v>442414</v>
       </c>
       <c r="R60" t="n">
-        <v>7027534</v>
+        <v>7027804</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7331,7 +7474,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7341,7 +7484,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7367,54 +7515,59 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
+          <t>https://artportalen.se/Sighting/135574611</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135851787</v>
+        <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>104815</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442360</v>
+        <v>442425</v>
       </c>
       <c r="R61" t="n">
-        <v>7027578</v>
+        <v>7027761</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,22 +7591,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,65 +7626,70 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
+          <t>https://artportalen.se/Sighting/135574612</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135851801</v>
+        <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>104815</v>
+        <v>57982</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442243</v>
+        <v>442455</v>
       </c>
       <c r="R62" t="n">
-        <v>7027546</v>
+        <v>7027671</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7550,22 +7713,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7580,65 +7748,70 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
+          <t>https://artportalen.se/Sighting/135574616</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135851775</v>
+        <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>100318</v>
+        <v>57982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222467</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442475</v>
+        <v>442432</v>
       </c>
       <c r="R63" t="n">
-        <v>7027687</v>
+        <v>7027650</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7662,22 +7835,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,74 +7870,70 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
+          <t>https://artportalen.se/Sighting/135574617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>55633849</v>
+        <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>101326</v>
+        <v>57982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442283</v>
+        <v>442465</v>
       </c>
       <c r="R64" t="n">
-        <v>7027836</v>
+        <v>7027665</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7783,17 +7957,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7804,58 +7988,53 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
+          <t>https://artportalen.se/Sighting/135574625</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574547</v>
+        <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>101502</v>
+        <v>57982</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7865,10 +8044,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442418</v>
+        <v>442550</v>
       </c>
       <c r="R65" t="n">
-        <v>7027847</v>
+        <v>7027681</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7900,7 +8079,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7910,7 +8089,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7936,58 +8120,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
+          <t>https://artportalen.se/Sighting/135574626</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5168927</v>
+        <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>98137</v>
+        <v>57982</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442283</v>
+        <v>442492</v>
       </c>
       <c r="R66" t="n">
-        <v>7027836</v>
+        <v>7027713</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8011,17 +8191,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8032,82 +8222,74 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
+          <t>https://artportalen.se/Sighting/135574627</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135851788</v>
+        <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>101392</v>
+        <v>57982</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442339</v>
+        <v>442502</v>
       </c>
       <c r="R67" t="n">
-        <v>7027583</v>
+        <v>7027719</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8131,22 +8313,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8155,77 +8342,68 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
+          <t>https://artportalen.se/Sighting/135574628</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851791</v>
+        <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>101392</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442312</v>
+        <v>442360</v>
       </c>
       <c r="R68" t="n">
-        <v>7027596</v>
+        <v>7027581</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8257,7 +8435,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8267,7 +8445,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8276,7 +8454,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8293,6 +8470,3451 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851785</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135851790</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>442323</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851790</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135851813</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>442444</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7027735</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851813</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135635857</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>442366</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135635857</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2596274</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2596274</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135574548</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7027839</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574548</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135574614</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>442464</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7027693</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574614</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135851773</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>442469</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7027704</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851773</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135851816</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7027780</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851816</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135574549</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574549</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135851772</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7027706</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851772</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135851793</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>442287</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851793</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135851800</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>442247</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851800</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135851804</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851804</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135851814</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>442453</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7027747</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851814</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135851815</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>442471</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7027763</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851815</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135851774</v>
+      </c>
+      <c r="B84" t="n">
+        <v>108387</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>442467</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7027703</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851774</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4041960</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4041960</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135851789</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106418</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>442341</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7027597</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851789</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135851806</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>442315</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7027602</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851806</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135851807</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>442368</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851807</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135851811</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>442432</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7027742</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851811</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135574569</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99320</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7027534</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574569</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135851787</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104815</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>442360</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7027578</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851787</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135851801</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104815</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>442243</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851801</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135851775</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100318</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>442475</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7027687</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851775</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>55633849</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55633849</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135574547</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>442418</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7027847</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574547</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5168927</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5168927</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135851788</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>442339</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7027583</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851788</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135851791</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>442312</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -8367,6 +11989,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135574586</v>
       </c>
       <c r="B6" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135574589</v>
       </c>
       <c r="B7" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135574591</v>
       </c>
       <c r="B8" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135574594</v>
       </c>
       <c r="B9" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135574597</v>
       </c>
       <c r="B10" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135574609</v>
       </c>
       <c r="B11" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135574620</v>
       </c>
       <c r="B12" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135574581</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135574623</v>
       </c>
       <c r="B14" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135574565</v>
       </c>
       <c r="B16" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96508</v>
+        <v>96509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96508</v>
+        <v>96509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135574562</v>
       </c>
       <c r="B23" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>135574545</v>
       </c>
       <c r="B25" t="n">
-        <v>93398</v>
+        <v>93399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93398</v>
+        <v>93399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93398</v>
+        <v>93399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93398</v>
+        <v>93399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135574548</v>
       </c>
       <c r="B73" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135574614</v>
       </c>
       <c r="B74" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>135574549</v>
       </c>
       <c r="B77" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>135574569</v>
       </c>
       <c r="B90" t="n">
-        <v>99320</v>
+        <v>99321</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100318</v>
+        <v>100320</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135574547</v>
       </c>
       <c r="B95" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135574555</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574543</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574570</v>
       </c>
       <c r="B4" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574571</v>
       </c>
       <c r="B5" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135574586</v>
       </c>
       <c r="B6" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135574589</v>
       </c>
       <c r="B7" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135574591</v>
       </c>
       <c r="B8" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135574594</v>
       </c>
       <c r="B9" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135574597</v>
       </c>
       <c r="B10" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135574609</v>
       </c>
       <c r="B11" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135574620</v>
       </c>
       <c r="B12" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135574581</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135574623</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>135574565</v>
       </c>
       <c r="B16" t="n">
-        <v>92409</v>
+        <v>92410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96509</v>
+        <v>96510</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96509</v>
+        <v>96510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135574562</v>
       </c>
       <c r="B23" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>135574545</v>
       </c>
       <c r="B25" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574538</v>
+        <v>135574556</v>
       </c>
       <c r="B37" t="n">
         <v>57982</v>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442449</v>
+        <v>442329</v>
       </c>
       <c r="R37" t="n">
-        <v>7027722</v>
+        <v>7027573</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574538</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574539</v>
+        <v>135851785</v>
       </c>
       <c r="B38" t="n">
         <v>57982</v>
@@ -4772,24 +4772,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442445</v>
+        <v>442360</v>
       </c>
       <c r="R38" t="n">
-        <v>7027731</v>
+        <v>7027581</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4813,27 +4808,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,24 +4838,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574539</t>
+          <t>https://artportalen.se/Sighting/135851785</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574540</v>
+        <v>135851790</v>
       </c>
       <c r="B39" t="n">
         <v>57982</v>
@@ -4894,24 +4884,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442421</v>
+        <v>442323</v>
       </c>
       <c r="R39" t="n">
-        <v>7027753</v>
+        <v>7027596</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4935,27 +4928,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4970,24 +4963,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574540</t>
+          <t>https://artportalen.se/Sighting/135851790</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574541</v>
+        <v>135851813</v>
       </c>
       <c r="B40" t="n">
         <v>57982</v>
@@ -5016,24 +5009,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442414</v>
+        <v>442444</v>
       </c>
       <c r="R40" t="n">
-        <v>7027802</v>
+        <v>7027735</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5057,27 +5053,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,27 +5088,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574541</t>
+          <t>https://artportalen.se/Sighting/135851813</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574542</v>
+        <v>135635857</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5120,27 +5116,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5149,13 +5152,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442437</v>
+        <v>442366</v>
       </c>
       <c r="R41" t="n">
-        <v>7027801</v>
+        <v>7027641</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,24 +5185,9 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5225,59 +5213,58 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574542</t>
+          <t>https://artportalen.se/Sighting/135635857</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574544</v>
+        <v>2596274</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>99017</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442430</v>
+        <v>442283</v>
       </c>
       <c r="R42" t="n">
-        <v>7027816</v>
+        <v>7027836</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5301,27 +5288,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5332,74 +5309,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574544</t>
+          <t>https://artportalen.se/Sighting/2596274</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574550</v>
+        <v>135574548</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>99297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442350</v>
+        <v>442411</v>
       </c>
       <c r="R43" t="n">
-        <v>7027791</v>
+        <v>7027839</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5428,7 +5405,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5438,12 +5415,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,38 +5441,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574550</t>
+          <t>https://artportalen.se/Sighting/135574548</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574551</v>
+        <v>135574614</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>99297</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5510,10 +5482,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442295</v>
+        <v>442464</v>
       </c>
       <c r="R44" t="n">
-        <v>7027775</v>
+        <v>7027693</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5545,7 +5517,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5555,12 +5527,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5586,58 +5553,62 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574551</t>
+          <t>https://artportalen.se/Sighting/135574614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574553</v>
+        <v>135851773</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>99297</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442327</v>
+        <v>442469</v>
       </c>
       <c r="R45" t="n">
-        <v>7027590</v>
+        <v>7027704</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5661,27 +5632,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,76 +5656,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574553</t>
+          <t>https://artportalen.se/Sighting/135851773</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574556</v>
+        <v>135851816</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>99297</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442329</v>
+        <v>442473</v>
       </c>
       <c r="R46" t="n">
-        <v>7027573</v>
+        <v>7027780</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5783,34 +5745,29 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5818,67 +5775,62 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135851816</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574558</v>
+        <v>135574549</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442329</v>
+        <v>442411</v>
       </c>
       <c r="R47" t="n">
-        <v>7027569</v>
+        <v>7027836</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5910,7 +5862,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5920,12 +5872,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5951,59 +5898,62 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574558</t>
+          <t>https://artportalen.se/Sighting/135574549</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574560</v>
+        <v>135851772</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442311</v>
+        <v>442473</v>
       </c>
       <c r="R48" t="n">
-        <v>7027581</v>
+        <v>7027706</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6027,27 +5977,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6056,76 +6001,72 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574560</t>
+          <t>https://artportalen.se/Sighting/135851772</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574561</v>
+        <v>135851793</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442291</v>
+        <v>442287</v>
       </c>
       <c r="R49" t="n">
-        <v>7027577</v>
+        <v>7027599</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,27 +6090,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6184,70 +6120,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574561</t>
+          <t>https://artportalen.se/Sighting/135851793</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574575</v>
+        <v>135851800</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442296</v>
+        <v>442247</v>
       </c>
       <c r="R50" t="n">
-        <v>7027551</v>
+        <v>7027546</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,27 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6306,69 +6232,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574575</t>
+          <t>https://artportalen.se/Sighting/135851800</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574580</v>
+        <v>135851804</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442295</v>
+        <v>442275</v>
       </c>
       <c r="R51" t="n">
-        <v>7027519</v>
+        <v>7027599</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6392,27 +6314,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,69 +6344,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574580</t>
+          <t>https://artportalen.se/Sighting/135851804</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574585</v>
+        <v>135851814</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442348</v>
+        <v>442453</v>
       </c>
       <c r="R52" t="n">
-        <v>7027560</v>
+        <v>7027747</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6513,27 +6426,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,70 +6456,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574585</t>
+          <t>https://artportalen.se/Sighting/135851814</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574587</v>
+        <v>135851815</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>99319</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442355</v>
+        <v>442471</v>
       </c>
       <c r="R53" t="n">
-        <v>7027577</v>
+        <v>7027763</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6635,27 +6538,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6670,70 +6568,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574587</t>
+          <t>https://artportalen.se/Sighting/135851815</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574590</v>
+        <v>135851774</v>
       </c>
       <c r="B54" t="n">
-        <v>57982</v>
+        <v>108390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442386</v>
+        <v>442467</v>
       </c>
       <c r="R54" t="n">
-        <v>7027567</v>
+        <v>7027703</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6757,27 +6650,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6792,65 +6680,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574590</t>
+          <t>https://artportalen.se/Sighting/135851774</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574593</v>
+        <v>4041960</v>
       </c>
       <c r="B55" t="n">
-        <v>57982</v>
+        <v>106229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442362</v>
+        <v>442283</v>
       </c>
       <c r="R55" t="n">
-        <v>7027657</v>
+        <v>7027836</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6874,27 +6766,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6905,74 +6787,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574593</t>
+          <t>https://artportalen.se/Sighting/4041960</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135574601</v>
+        <v>135851789</v>
       </c>
       <c r="B56" t="n">
-        <v>57982</v>
+        <v>106421</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442387</v>
+        <v>442341</v>
       </c>
       <c r="R56" t="n">
-        <v>7027641</v>
+        <v>7027597</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,27 +6878,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7031,65 +6908,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574601</t>
+          <t>https://artportalen.se/Sighting/135851789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135574605</v>
+        <v>135851806</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442416</v>
+        <v>442315</v>
       </c>
       <c r="R57" t="n">
-        <v>7027567</v>
+        <v>7027602</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,27 +6990,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7148,70 +7020,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574605</t>
+          <t>https://artportalen.se/Sighting/135851806</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135574608</v>
+        <v>135851807</v>
       </c>
       <c r="B58" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442410</v>
+        <v>442368</v>
       </c>
       <c r="R58" t="n">
-        <v>7027707</v>
+        <v>7027641</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7235,27 +7102,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7270,65 +7132,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574608</t>
+          <t>https://artportalen.se/Sighting/135851807</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135574610</v>
+        <v>135851811</v>
       </c>
       <c r="B59" t="n">
-        <v>57982</v>
+        <v>99317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442382</v>
+        <v>442432</v>
       </c>
       <c r="R59" t="n">
-        <v>7027768</v>
+        <v>7027742</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7352,27 +7214,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7387,49 +7244,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574610</t>
+          <t>https://artportalen.se/Sighting/135851811</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574611</v>
+        <v>135574569</v>
       </c>
       <c r="B60" t="n">
-        <v>57982</v>
+        <v>99322</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>222118</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7439,10 +7296,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442414</v>
+        <v>442283</v>
       </c>
       <c r="R60" t="n">
-        <v>7027804</v>
+        <v>7027534</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7474,7 +7331,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7484,12 +7341,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7515,59 +7367,54 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574611</t>
+          <t>https://artportalen.se/Sighting/135574569</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135574612</v>
+        <v>135851787</v>
       </c>
       <c r="B61" t="n">
-        <v>57982</v>
+        <v>104818</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442425</v>
+        <v>442360</v>
       </c>
       <c r="R61" t="n">
-        <v>7027761</v>
+        <v>7027578</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7591,27 +7438,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7626,70 +7468,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574612</t>
+          <t>https://artportalen.se/Sighting/135851787</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135574616</v>
+        <v>135851801</v>
       </c>
       <c r="B62" t="n">
-        <v>57982</v>
+        <v>104818</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442455</v>
+        <v>442243</v>
       </c>
       <c r="R62" t="n">
-        <v>7027671</v>
+        <v>7027546</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7713,27 +7550,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7748,70 +7580,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574616</t>
+          <t>https://artportalen.se/Sighting/135851801</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135574617</v>
+        <v>135851775</v>
       </c>
       <c r="B63" t="n">
-        <v>57982</v>
+        <v>100321</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442432</v>
+        <v>442475</v>
       </c>
       <c r="R63" t="n">
-        <v>7027650</v>
+        <v>7027687</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,27 +7662,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7870,70 +7692,74 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574617</t>
+          <t>https://artportalen.se/Sighting/135851775</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135574625</v>
+        <v>55633849</v>
       </c>
       <c r="B64" t="n">
-        <v>57982</v>
+        <v>101326</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442465</v>
+        <v>442283</v>
       </c>
       <c r="R64" t="n">
-        <v>7027665</v>
+        <v>7027836</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7957,27 +7783,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7988,53 +7804,58 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574625</t>
+          <t>https://artportalen.se/Sighting/55633849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574626</v>
+        <v>135574547</v>
       </c>
       <c r="B65" t="n">
-        <v>57982</v>
+        <v>101505</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8044,10 +7865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442550</v>
+        <v>442418</v>
       </c>
       <c r="R65" t="n">
-        <v>7027681</v>
+        <v>7027847</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8079,7 +7900,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8089,12 +7910,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8120,54 +7936,58 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574626</t>
+          <t>https://artportalen.se/Sighting/135574547</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135574627</v>
+        <v>5168927</v>
       </c>
       <c r="B66" t="n">
-        <v>57982</v>
+        <v>98137</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442492</v>
+        <v>442283</v>
       </c>
       <c r="R66" t="n">
-        <v>7027713</v>
+        <v>7027836</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8191,27 +8011,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8222,74 +8032,82 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574627</t>
+          <t>https://artportalen.se/Sighting/5168927</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135574628</v>
+        <v>135851788</v>
       </c>
       <c r="B67" t="n">
-        <v>57982</v>
+        <v>101395</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442502</v>
+        <v>442339</v>
       </c>
       <c r="R67" t="n">
-        <v>7027719</v>
+        <v>7027583</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8313,27 +8131,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8342,68 +8155,77 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574628</t>
+          <t>https://artportalen.se/Sighting/135851788</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851785</v>
+        <v>135851791</v>
       </c>
       <c r="B68" t="n">
-        <v>57982</v>
+        <v>101395</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442360</v>
+        <v>442312</v>
       </c>
       <c r="R68" t="n">
-        <v>7027581</v>
+        <v>7027596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8435,7 +8257,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8445,7 +8267,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,6 +8276,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8470,3451 +8293,6 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135851790</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>442323</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135851813</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>442444</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7027735</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135635857</v>
-      </c>
-      <c r="B71" t="n">
-        <v>58143</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>442366</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2596274</v>
-      </c>
-      <c r="B72" t="n">
-        <v>99017</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>219795</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Grönkulla</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135574548</v>
-      </c>
-      <c r="B73" t="n">
-        <v>99296</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7027839</v>
-      </c>
-      <c r="S73" t="n">
-        <v>3</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135574614</v>
-      </c>
-      <c r="B74" t="n">
-        <v>99296</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>442464</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7027693</v>
-      </c>
-      <c r="S74" t="n">
-        <v>3</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135851773</v>
-      </c>
-      <c r="B75" t="n">
-        <v>99296</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>442469</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7027704</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135851816</v>
-      </c>
-      <c r="B76" t="n">
-        <v>99296</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7027780</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135574549</v>
-      </c>
-      <c r="B77" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135851772</v>
-      </c>
-      <c r="B78" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7027706</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135851793</v>
-      </c>
-      <c r="B79" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>442287</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135851800</v>
-      </c>
-      <c r="B80" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>442247</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135851804</v>
-      </c>
-      <c r="B81" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135851814</v>
-      </c>
-      <c r="B82" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>442453</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7027747</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135851815</v>
-      </c>
-      <c r="B83" t="n">
-        <v>99318</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>442471</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7027763</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135851774</v>
-      </c>
-      <c r="B84" t="n">
-        <v>108389</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>220102</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Kärrfibbla</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Crepis paludosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>442467</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7027703</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>4041960</v>
-      </c>
-      <c r="B85" t="n">
-        <v>106229</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135851789</v>
-      </c>
-      <c r="B86" t="n">
-        <v>106420</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>442341</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7027597</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135851806</v>
-      </c>
-      <c r="B87" t="n">
-        <v>99316</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>442315</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7027602</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135851807</v>
-      </c>
-      <c r="B88" t="n">
-        <v>99316</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>442368</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135851811</v>
-      </c>
-      <c r="B89" t="n">
-        <v>99316</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>442432</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7027742</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135574569</v>
-      </c>
-      <c r="B90" t="n">
-        <v>99321</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>222118</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Flugblomster</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Ophrys insectifera</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7027534</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135851787</v>
-      </c>
-      <c r="B91" t="n">
-        <v>104817</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>442360</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7027578</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135851801</v>
-      </c>
-      <c r="B92" t="n">
-        <v>104817</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>442243</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135851775</v>
-      </c>
-      <c r="B93" t="n">
-        <v>100320</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>222467</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gräsull</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>442475</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7027687</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>55633849</v>
-      </c>
-      <c r="B94" t="n">
-        <v>101326</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135574547</v>
-      </c>
-      <c r="B95" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>442418</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7027847</v>
-      </c>
-      <c r="S95" t="n">
-        <v>3</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5168927</v>
-      </c>
-      <c r="B96" t="n">
-        <v>98137</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>222741</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Finbräken</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Cystopteris montana</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135851788</v>
-      </c>
-      <c r="B97" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>442339</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7027583</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>135851791</v>
-      </c>
-      <c r="B98" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>442312</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -11989,36 +8367,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574556</v>
+        <v>135574538</v>
       </c>
       <c r="B37" t="n">
         <v>57982</v>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442329</v>
+        <v>442449</v>
       </c>
       <c r="R37" t="n">
-        <v>7027573</v>
+        <v>7027722</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135574538</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135851785</v>
+        <v>135574539</v>
       </c>
       <c r="B38" t="n">
         <v>57982</v>
@@ -4772,19 +4772,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442360</v>
+        <v>442445</v>
       </c>
       <c r="R38" t="n">
-        <v>7027581</v>
+        <v>7027731</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4808,22 +4813,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,24 +4848,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
+          <t>https://artportalen.se/Sighting/135574539</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135851790</v>
+        <v>135574540</v>
       </c>
       <c r="B39" t="n">
         <v>57982</v>
@@ -4884,27 +4894,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442323</v>
+        <v>442421</v>
       </c>
       <c r="R39" t="n">
-        <v>7027596</v>
+        <v>7027753</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4928,27 +4935,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,24 +4970,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
+          <t>https://artportalen.se/Sighting/135574540</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135851813</v>
+        <v>135574541</v>
       </c>
       <c r="B40" t="n">
         <v>57982</v>
@@ -5009,27 +5016,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442444</v>
+        <v>442414</v>
       </c>
       <c r="R40" t="n">
-        <v>7027735</v>
+        <v>7027802</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5053,27 +5057,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,27 +5092,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
+          <t>https://artportalen.se/Sighting/135574541</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135635857</v>
+        <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,34 +5120,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5152,13 +5149,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442366</v>
+        <v>442437</v>
       </c>
       <c r="R41" t="n">
-        <v>7027641</v>
+        <v>7027801</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5185,9 +5182,24 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,58 +5225,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
+          <t>https://artportalen.se/Sighting/135574542</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2596274</v>
+        <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>99017</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442283</v>
+        <v>442430</v>
       </c>
       <c r="R42" t="n">
-        <v>7027836</v>
+        <v>7027816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5288,17 +5301,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,74 +5332,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
+          <t>https://artportalen.se/Sighting/135574544</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574548</v>
+        <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>99297</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442411</v>
+        <v>442350</v>
       </c>
       <c r="R43" t="n">
-        <v>7027839</v>
+        <v>7027791</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,7 +5428,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5415,7 +5438,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,38 +5469,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
+          <t>https://artportalen.se/Sighting/135574550</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574614</v>
+        <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>99297</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5482,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442464</v>
+        <v>442295</v>
       </c>
       <c r="R44" t="n">
-        <v>7027693</v>
+        <v>7027775</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5517,7 +5545,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5527,7 +5555,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5553,62 +5586,58 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
+          <t>https://artportalen.se/Sighting/135574551</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135851773</v>
+        <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>99297</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442469</v>
+        <v>442327</v>
       </c>
       <c r="R45" t="n">
-        <v>7027704</v>
+        <v>7027590</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5632,22 +5661,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5656,72 +5690,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
+          <t>https://artportalen.se/Sighting/135574553</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135851816</v>
+        <v>135574556</v>
       </c>
       <c r="B46" t="n">
-        <v>99297</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442473</v>
+        <v>442329</v>
       </c>
       <c r="R46" t="n">
-        <v>7027780</v>
+        <v>7027573</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5745,29 +5783,34 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5775,62 +5818,67 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574549</v>
+        <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442411</v>
+        <v>442329</v>
       </c>
       <c r="R47" t="n">
-        <v>7027836</v>
+        <v>7027569</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5862,7 +5910,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5872,7 +5920,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5898,62 +5951,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
+          <t>https://artportalen.se/Sighting/135574558</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135851772</v>
+        <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442473</v>
+        <v>442311</v>
       </c>
       <c r="R48" t="n">
-        <v>7027706</v>
+        <v>7027581</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5977,22 +6027,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,72 +6056,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
+          <t>https://artportalen.se/Sighting/135574560</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135851793</v>
+        <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442287</v>
+        <v>442291</v>
       </c>
       <c r="R49" t="n">
-        <v>7027599</v>
+        <v>7027577</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6090,22 +6149,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6120,65 +6184,70 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
+          <t>https://artportalen.se/Sighting/135574561</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135851800</v>
+        <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442247</v>
+        <v>442296</v>
       </c>
       <c r="R50" t="n">
-        <v>7027546</v>
+        <v>7027551</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6271,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,65 +6306,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
+          <t>https://artportalen.se/Sighting/135574575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135851804</v>
+        <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442275</v>
+        <v>442295</v>
       </c>
       <c r="R51" t="n">
-        <v>7027599</v>
+        <v>7027519</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6314,22 +6392,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6344,65 +6427,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
+          <t>https://artportalen.se/Sighting/135574580</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135851814</v>
+        <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442453</v>
+        <v>442348</v>
       </c>
       <c r="R52" t="n">
-        <v>7027747</v>
+        <v>7027560</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6426,22 +6513,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6456,65 +6548,70 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
+          <t>https://artportalen.se/Sighting/135574585</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135851815</v>
+        <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>99319</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442471</v>
+        <v>442355</v>
       </c>
       <c r="R53" t="n">
-        <v>7027763</v>
+        <v>7027577</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,22 +6635,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6568,65 +6670,70 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
+          <t>https://artportalen.se/Sighting/135574587</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135851774</v>
+        <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>108390</v>
+        <v>57982</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442467</v>
+        <v>442386</v>
       </c>
       <c r="R54" t="n">
-        <v>7027703</v>
+        <v>7027567</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6650,22 +6757,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6680,69 +6792,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
+          <t>https://artportalen.se/Sighting/135574590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4041960</v>
+        <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>106229</v>
+        <v>57982</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442283</v>
+        <v>442362</v>
       </c>
       <c r="R55" t="n">
-        <v>7027836</v>
+        <v>7027657</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6766,17 +6874,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6787,74 +6905,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
+          <t>https://artportalen.se/Sighting/135574593</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135851789</v>
+        <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>106421</v>
+        <v>57982</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442341</v>
+        <v>442387</v>
       </c>
       <c r="R56" t="n">
-        <v>7027597</v>
+        <v>7027641</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6878,22 +6996,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6908,65 +7031,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
+          <t>https://artportalen.se/Sighting/135574601</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135851806</v>
+        <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442315</v>
+        <v>442416</v>
       </c>
       <c r="R57" t="n">
-        <v>7027602</v>
+        <v>7027567</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6990,22 +7113,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7020,65 +7148,70 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
+          <t>https://artportalen.se/Sighting/135574605</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135851807</v>
+        <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442368</v>
+        <v>442410</v>
       </c>
       <c r="R58" t="n">
-        <v>7027641</v>
+        <v>7027707</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7102,22 +7235,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7132,65 +7270,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
+          <t>https://artportalen.se/Sighting/135574608</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135851811</v>
+        <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442432</v>
+        <v>442382</v>
       </c>
       <c r="R59" t="n">
-        <v>7027742</v>
+        <v>7027768</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,22 +7352,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,49 +7387,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
+          <t>https://artportalen.se/Sighting/135574610</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574569</v>
+        <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>99322</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222118</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7296,10 +7439,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442283</v>
+        <v>442414</v>
       </c>
       <c r="R60" t="n">
-        <v>7027534</v>
+        <v>7027804</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7331,7 +7474,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7341,7 +7484,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7367,54 +7515,59 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
+          <t>https://artportalen.se/Sighting/135574611</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135851787</v>
+        <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>104818</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442360</v>
+        <v>442425</v>
       </c>
       <c r="R61" t="n">
-        <v>7027578</v>
+        <v>7027761</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,22 +7591,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,65 +7626,70 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
+          <t>https://artportalen.se/Sighting/135574612</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135851801</v>
+        <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>104818</v>
+        <v>57982</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442243</v>
+        <v>442455</v>
       </c>
       <c r="R62" t="n">
-        <v>7027546</v>
+        <v>7027671</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7550,22 +7713,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7580,65 +7748,70 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
+          <t>https://artportalen.se/Sighting/135574616</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135851775</v>
+        <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>100321</v>
+        <v>57982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222467</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442475</v>
+        <v>442432</v>
       </c>
       <c r="R63" t="n">
-        <v>7027687</v>
+        <v>7027650</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7662,22 +7835,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,74 +7870,70 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
+          <t>https://artportalen.se/Sighting/135574617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>55633849</v>
+        <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>101326</v>
+        <v>57982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442283</v>
+        <v>442465</v>
       </c>
       <c r="R64" t="n">
-        <v>7027836</v>
+        <v>7027665</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7783,17 +7957,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7804,58 +7988,53 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
+          <t>https://artportalen.se/Sighting/135574625</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574547</v>
+        <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>101505</v>
+        <v>57982</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7865,10 +8044,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442418</v>
+        <v>442550</v>
       </c>
       <c r="R65" t="n">
-        <v>7027847</v>
+        <v>7027681</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7900,7 +8079,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7910,7 +8089,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7936,58 +8120,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
+          <t>https://artportalen.se/Sighting/135574626</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5168927</v>
+        <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>98137</v>
+        <v>57982</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442283</v>
+        <v>442492</v>
       </c>
       <c r="R66" t="n">
-        <v>7027836</v>
+        <v>7027713</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8011,17 +8191,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8032,82 +8222,74 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
+          <t>https://artportalen.se/Sighting/135574627</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135851788</v>
+        <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>101395</v>
+        <v>57982</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442339</v>
+        <v>442502</v>
       </c>
       <c r="R67" t="n">
-        <v>7027583</v>
+        <v>7027719</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8131,22 +8313,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8155,77 +8342,68 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
+          <t>https://artportalen.se/Sighting/135574628</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851791</v>
+        <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>101395</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442312</v>
+        <v>442360</v>
       </c>
       <c r="R68" t="n">
-        <v>7027596</v>
+        <v>7027581</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8257,7 +8435,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8267,7 +8445,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8276,7 +8454,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8293,6 +8470,3451 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851785</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135851790</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>442323</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851790</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135851813</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>442444</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7027735</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851813</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135635857</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>442366</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135635857</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2596274</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2596274</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135574548</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99297</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7027839</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574548</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135574614</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99297</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>442464</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7027693</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574614</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135851773</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99297</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>442469</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7027704</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851773</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135851816</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99297</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7027780</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851816</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135574549</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574549</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135851772</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7027706</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851772</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135851793</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>442287</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851793</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135851800</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>442247</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851800</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135851804</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851804</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135851814</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>442453</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7027747</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851814</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135851815</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>442471</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7027763</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851815</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135851774</v>
+      </c>
+      <c r="B84" t="n">
+        <v>108390</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>442467</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7027703</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851774</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4041960</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4041960</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135851789</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106421</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>442341</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7027597</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851789</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135851806</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>442315</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7027602</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851806</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135851807</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>442368</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851807</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135851811</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>442432</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7027742</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851811</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135574569</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99322</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7027534</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574569</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135851787</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104818</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>442360</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7027578</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851787</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135851801</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104818</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>442243</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851801</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135851775</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100321</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>442475</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7027687</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851775</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>55633849</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55633849</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135574547</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>442418</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7027847</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574547</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5168927</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5168927</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135851788</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>442339</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7027583</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851788</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135851791</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>442312</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -8367,6 +11989,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96510</v>
+        <v>96511</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96510</v>
+        <v>96511</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93400</v>
+        <v>93401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93400</v>
+        <v>93401</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93400</v>
+        <v>93401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135574538</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>135574539</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>135574540</v>
       </c>
       <c r="B39" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135574541</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>135851790</v>
       </c>
       <c r="B69" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>135851813</v>
       </c>
       <c r="B70" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>135635857</v>
       </c>
       <c r="B71" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99297</v>
+        <v>99298</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99297</v>
+        <v>99298</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100321</v>
+        <v>100322</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96511</v>
+        <v>96517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96511</v>
+        <v>96517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91587</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93401</v>
+        <v>93407</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93401</v>
+        <v>93407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93401</v>
+        <v>93407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135574538</v>
       </c>
       <c r="B37" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>135574539</v>
       </c>
       <c r="B38" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>135574540</v>
       </c>
       <c r="B39" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135574541</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>135851790</v>
       </c>
       <c r="B69" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>135851813</v>
       </c>
       <c r="B70" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>135635857</v>
       </c>
       <c r="B71" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99298</v>
+        <v>99304</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99298</v>
+        <v>99304</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100322</v>
+        <v>100328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96517</v>
+        <v>96518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96517</v>
+        <v>96518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>91594</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135574538</v>
       </c>
       <c r="B37" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>135574539</v>
       </c>
       <c r="B38" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>135574540</v>
       </c>
       <c r="B39" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135574541</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>135851790</v>
       </c>
       <c r="B69" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>135851813</v>
       </c>
       <c r="B70" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99304</v>
+        <v>99305</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99304</v>
+        <v>99305</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100328</v>
+        <v>100329</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96518</v>
+        <v>96529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96518</v>
+        <v>96529</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99305</v>
+        <v>99316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99305</v>
+        <v>99316</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100329</v>
+        <v>100340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96529</v>
+        <v>96542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96529</v>
+        <v>96542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93414</v>
+        <v>93421</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93414</v>
+        <v>93421</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93414</v>
+        <v>93421</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135574538</v>
       </c>
       <c r="B37" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>135574539</v>
       </c>
       <c r="B38" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>135574540</v>
       </c>
       <c r="B39" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135574541</v>
       </c>
       <c r="B40" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>135851790</v>
       </c>
       <c r="B69" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>135851813</v>
       </c>
       <c r="B70" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99316</v>
+        <v>99329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99316</v>
+        <v>99329</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100340</v>
+        <v>100353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96542</v>
+        <v>96543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96542</v>
+        <v>96543</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100353</v>
+        <v>100354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96543</v>
+        <v>96556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96543</v>
+        <v>96556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91608</v>
+        <v>91621</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,10 +4621,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574538</v>
+        <v>135574556</v>
       </c>
       <c r="B37" t="n">
-        <v>57993</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442449</v>
+        <v>442329</v>
       </c>
       <c r="R37" t="n">
-        <v>7027722</v>
+        <v>7027573</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,16 +4737,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574538</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574539</v>
+        <v>135851785</v>
       </c>
       <c r="B38" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4772,24 +4772,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442445</v>
+        <v>442360</v>
       </c>
       <c r="R38" t="n">
-        <v>7027731</v>
+        <v>7027581</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4813,27 +4808,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,27 +4838,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574539</t>
+          <t>https://artportalen.se/Sighting/135851785</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574540</v>
+        <v>135851790</v>
       </c>
       <c r="B39" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,24 +4884,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442421</v>
+        <v>442323</v>
       </c>
       <c r="R39" t="n">
-        <v>7027753</v>
+        <v>7027596</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4935,27 +4928,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4970,27 +4963,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574540</t>
+          <t>https://artportalen.se/Sighting/135851790</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574541</v>
+        <v>135851813</v>
       </c>
       <c r="B40" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5016,24 +5009,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442414</v>
+        <v>442444</v>
       </c>
       <c r="R40" t="n">
-        <v>7027802</v>
+        <v>7027735</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5057,27 +5053,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,27 +5088,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574541</t>
+          <t>https://artportalen.se/Sighting/135851813</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574542</v>
+        <v>135635857</v>
       </c>
       <c r="B41" t="n">
-        <v>57993</v>
+        <v>58148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5120,27 +5116,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5149,13 +5152,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442437</v>
+        <v>442366</v>
       </c>
       <c r="R41" t="n">
-        <v>7027801</v>
+        <v>7027641</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,24 +5185,9 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5225,59 +5213,58 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574542</t>
+          <t>https://artportalen.se/Sighting/135635857</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574544</v>
+        <v>2596274</v>
       </c>
       <c r="B42" t="n">
-        <v>57993</v>
+        <v>99017</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442430</v>
+        <v>442283</v>
       </c>
       <c r="R42" t="n">
-        <v>7027816</v>
+        <v>7027836</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5301,27 +5288,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5332,74 +5309,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574544</t>
+          <t>https://artportalen.se/Sighting/2596274</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574550</v>
+        <v>135574548</v>
       </c>
       <c r="B43" t="n">
-        <v>57993</v>
+        <v>99297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442350</v>
+        <v>442411</v>
       </c>
       <c r="R43" t="n">
-        <v>7027791</v>
+        <v>7027839</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5428,7 +5405,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5438,12 +5415,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,38 +5441,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574550</t>
+          <t>https://artportalen.se/Sighting/135574548</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574551</v>
+        <v>135574614</v>
       </c>
       <c r="B44" t="n">
-        <v>57993</v>
+        <v>99297</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5510,10 +5482,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442295</v>
+        <v>442464</v>
       </c>
       <c r="R44" t="n">
-        <v>7027775</v>
+        <v>7027693</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5545,7 +5517,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5555,12 +5527,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5586,58 +5553,62 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574551</t>
+          <t>https://artportalen.se/Sighting/135574614</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574553</v>
+        <v>135851773</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>99343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442327</v>
+        <v>442469</v>
       </c>
       <c r="R45" t="n">
-        <v>7027590</v>
+        <v>7027704</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5661,27 +5632,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,76 +5656,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574553</t>
+          <t>https://artportalen.se/Sighting/135851773</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574556</v>
+        <v>135851816</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>99343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442329</v>
+        <v>442473</v>
       </c>
       <c r="R46" t="n">
-        <v>7027573</v>
+        <v>7027780</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5783,34 +5745,29 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5818,67 +5775,62 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135851816</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574558</v>
+        <v>135574549</v>
       </c>
       <c r="B47" t="n">
-        <v>57993</v>
+        <v>99319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442329</v>
+        <v>442411</v>
       </c>
       <c r="R47" t="n">
-        <v>7027569</v>
+        <v>7027836</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5910,7 +5862,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5920,12 +5872,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5951,59 +5898,62 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574558</t>
+          <t>https://artportalen.se/Sighting/135574549</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574560</v>
+        <v>135851772</v>
       </c>
       <c r="B48" t="n">
-        <v>57993</v>
+        <v>99365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442311</v>
+        <v>442473</v>
       </c>
       <c r="R48" t="n">
-        <v>7027581</v>
+        <v>7027706</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6027,27 +5977,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6056,76 +6001,72 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574560</t>
+          <t>https://artportalen.se/Sighting/135851772</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574561</v>
+        <v>135851793</v>
       </c>
       <c r="B49" t="n">
-        <v>57993</v>
+        <v>99365</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442291</v>
+        <v>442287</v>
       </c>
       <c r="R49" t="n">
-        <v>7027577</v>
+        <v>7027599</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,27 +6090,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6184,70 +6120,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574561</t>
+          <t>https://artportalen.se/Sighting/135851793</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574575</v>
+        <v>135851800</v>
       </c>
       <c r="B50" t="n">
-        <v>57993</v>
+        <v>99365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442296</v>
+        <v>442247</v>
       </c>
       <c r="R50" t="n">
-        <v>7027551</v>
+        <v>7027546</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,27 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6306,69 +6232,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574575</t>
+          <t>https://artportalen.se/Sighting/135851800</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574580</v>
+        <v>135851804</v>
       </c>
       <c r="B51" t="n">
-        <v>57993</v>
+        <v>99365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442295</v>
+        <v>442275</v>
       </c>
       <c r="R51" t="n">
-        <v>7027519</v>
+        <v>7027599</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6392,27 +6314,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,69 +6344,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574580</t>
+          <t>https://artportalen.se/Sighting/135851804</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574585</v>
+        <v>135851814</v>
       </c>
       <c r="B52" t="n">
-        <v>57993</v>
+        <v>99365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442348</v>
+        <v>442453</v>
       </c>
       <c r="R52" t="n">
-        <v>7027560</v>
+        <v>7027747</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6513,27 +6426,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,70 +6456,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574585</t>
+          <t>https://artportalen.se/Sighting/135851814</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574587</v>
+        <v>135851815</v>
       </c>
       <c r="B53" t="n">
-        <v>57993</v>
+        <v>99365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442355</v>
+        <v>442471</v>
       </c>
       <c r="R53" t="n">
-        <v>7027577</v>
+        <v>7027763</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6635,27 +6538,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6670,70 +6568,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574587</t>
+          <t>https://artportalen.se/Sighting/135851815</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574590</v>
+        <v>135851774</v>
       </c>
       <c r="B54" t="n">
-        <v>57993</v>
+        <v>108436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442386</v>
+        <v>442467</v>
       </c>
       <c r="R54" t="n">
-        <v>7027567</v>
+        <v>7027703</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6757,27 +6650,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6792,65 +6680,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574590</t>
+          <t>https://artportalen.se/Sighting/135851774</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574593</v>
+        <v>4041960</v>
       </c>
       <c r="B55" t="n">
-        <v>57993</v>
+        <v>106229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442362</v>
+        <v>442283</v>
       </c>
       <c r="R55" t="n">
-        <v>7027657</v>
+        <v>7027836</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6874,27 +6766,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6905,74 +6787,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574593</t>
+          <t>https://artportalen.se/Sighting/4041960</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135574601</v>
+        <v>135851789</v>
       </c>
       <c r="B56" t="n">
-        <v>57993</v>
+        <v>106467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442387</v>
+        <v>442341</v>
       </c>
       <c r="R56" t="n">
-        <v>7027641</v>
+        <v>7027597</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,27 +6878,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7031,65 +6908,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574601</t>
+          <t>https://artportalen.se/Sighting/135851789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135574605</v>
+        <v>135851806</v>
       </c>
       <c r="B57" t="n">
-        <v>57993</v>
+        <v>99363</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442416</v>
+        <v>442315</v>
       </c>
       <c r="R57" t="n">
-        <v>7027567</v>
+        <v>7027602</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,27 +6990,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7148,70 +7020,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574605</t>
+          <t>https://artportalen.se/Sighting/135851806</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135574608</v>
+        <v>135851807</v>
       </c>
       <c r="B58" t="n">
-        <v>57993</v>
+        <v>99363</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442410</v>
+        <v>442368</v>
       </c>
       <c r="R58" t="n">
-        <v>7027707</v>
+        <v>7027641</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7235,27 +7102,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7270,65 +7132,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574608</t>
+          <t>https://artportalen.se/Sighting/135851807</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135574610</v>
+        <v>135851811</v>
       </c>
       <c r="B59" t="n">
-        <v>57993</v>
+        <v>99363</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442382</v>
+        <v>442432</v>
       </c>
       <c r="R59" t="n">
-        <v>7027768</v>
+        <v>7027742</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7352,27 +7214,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7387,49 +7244,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574610</t>
+          <t>https://artportalen.se/Sighting/135851811</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574611</v>
+        <v>135574569</v>
       </c>
       <c r="B60" t="n">
-        <v>57993</v>
+        <v>99322</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>222118</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7439,10 +7296,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442414</v>
+        <v>442283</v>
       </c>
       <c r="R60" t="n">
-        <v>7027804</v>
+        <v>7027534</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7474,7 +7331,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7484,12 +7341,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7515,59 +7367,54 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574611</t>
+          <t>https://artportalen.se/Sighting/135574569</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135574612</v>
+        <v>135851787</v>
       </c>
       <c r="B61" t="n">
-        <v>57993</v>
+        <v>104864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442425</v>
+        <v>442360</v>
       </c>
       <c r="R61" t="n">
-        <v>7027761</v>
+        <v>7027578</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7591,27 +7438,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7626,70 +7468,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574612</t>
+          <t>https://artportalen.se/Sighting/135851787</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135574616</v>
+        <v>135851801</v>
       </c>
       <c r="B62" t="n">
-        <v>57993</v>
+        <v>104864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442455</v>
+        <v>442243</v>
       </c>
       <c r="R62" t="n">
-        <v>7027671</v>
+        <v>7027546</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7713,27 +7550,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7748,70 +7580,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574616</t>
+          <t>https://artportalen.se/Sighting/135851801</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135574617</v>
+        <v>135851775</v>
       </c>
       <c r="B63" t="n">
-        <v>57993</v>
+        <v>100367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442432</v>
+        <v>442475</v>
       </c>
       <c r="R63" t="n">
-        <v>7027650</v>
+        <v>7027687</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,27 +7662,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7870,70 +7692,74 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574617</t>
+          <t>https://artportalen.se/Sighting/135851775</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135574625</v>
+        <v>55633849</v>
       </c>
       <c r="B64" t="n">
-        <v>57993</v>
+        <v>101326</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442465</v>
+        <v>442283</v>
       </c>
       <c r="R64" t="n">
-        <v>7027665</v>
+        <v>7027836</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7957,27 +7783,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7988,53 +7804,58 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574625</t>
+          <t>https://artportalen.se/Sighting/55633849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574626</v>
+        <v>135574547</v>
       </c>
       <c r="B65" t="n">
-        <v>57993</v>
+        <v>101505</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8044,10 +7865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442550</v>
+        <v>442418</v>
       </c>
       <c r="R65" t="n">
-        <v>7027681</v>
+        <v>7027847</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8079,7 +7900,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8089,12 +7910,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8120,54 +7936,58 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574626</t>
+          <t>https://artportalen.se/Sighting/135574547</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135574627</v>
+        <v>5168927</v>
       </c>
       <c r="B66" t="n">
-        <v>57993</v>
+        <v>98137</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Storbrännan /700 m SV/, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442492</v>
+        <v>442283</v>
       </c>
       <c r="R66" t="n">
-        <v>7027713</v>
+        <v>7027836</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8191,27 +8011,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2001-07-25</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>taxyta Ö1000</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8222,74 +8032,82 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisbeth Berntsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574627</t>
+          <t>https://artportalen.se/Sighting/5168927</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135574628</v>
+        <v>135851788</v>
       </c>
       <c r="B67" t="n">
-        <v>57993</v>
+        <v>101441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storbrännan sv, Jmt</t>
+          <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442502</v>
+        <v>442339</v>
       </c>
       <c r="R67" t="n">
-        <v>7027719</v>
+        <v>7027583</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8313,27 +8131,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8342,68 +8155,77 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574628</t>
+          <t>https://artportalen.se/Sighting/135851788</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851785</v>
+        <v>135851791</v>
       </c>
       <c r="B68" t="n">
-        <v>57993</v>
+        <v>101441</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>224885</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442360</v>
+        <v>442312</v>
       </c>
       <c r="R68" t="n">
-        <v>7027581</v>
+        <v>7027596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8435,7 +8257,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8445,7 +8267,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,6 +8276,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8470,3451 +8293,6 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135851790</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>442323</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135851813</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>442444</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7027735</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135635857</v>
-      </c>
-      <c r="B71" t="n">
-        <v>58148</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>442366</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2596274</v>
-      </c>
-      <c r="B72" t="n">
-        <v>99017</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>219795</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Grönkulla</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135574548</v>
-      </c>
-      <c r="B73" t="n">
-        <v>99297</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7027839</v>
-      </c>
-      <c r="S73" t="n">
-        <v>3</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135574614</v>
-      </c>
-      <c r="B74" t="n">
-        <v>99297</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>442464</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7027693</v>
-      </c>
-      <c r="S74" t="n">
-        <v>3</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135851773</v>
-      </c>
-      <c r="B75" t="n">
-        <v>99330</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>442469</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7027704</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135851816</v>
-      </c>
-      <c r="B76" t="n">
-        <v>99330</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7027780</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135574549</v>
-      </c>
-      <c r="B77" t="n">
-        <v>99319</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>442411</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135851772</v>
-      </c>
-      <c r="B78" t="n">
-        <v>99352</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>442473</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7027706</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135851793</v>
-      </c>
-      <c r="B79" t="n">
-        <v>99352</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>442287</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135851800</v>
-      </c>
-      <c r="B80" t="n">
-        <v>99352</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>442247</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135851804</v>
-      </c>
-      <c r="B81" t="n">
-        <v>99352</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>442275</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7027599</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135851814</v>
-      </c>
-      <c r="B82" t="n">
-        <v>99352</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>442453</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7027747</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135851815</v>
-      </c>
-      <c r="B83" t="n">
-        <v>99352</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>442471</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7027763</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135851774</v>
-      </c>
-      <c r="B84" t="n">
-        <v>108423</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>220102</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Kärrfibbla</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Crepis paludosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>442467</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7027703</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>4041960</v>
-      </c>
-      <c r="B85" t="n">
-        <v>106229</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135851789</v>
-      </c>
-      <c r="B86" t="n">
-        <v>106454</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>442341</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7027597</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135851806</v>
-      </c>
-      <c r="B87" t="n">
-        <v>99350</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>442315</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7027602</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>20:02</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135851807</v>
-      </c>
-      <c r="B88" t="n">
-        <v>99350</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>442368</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7027641</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135851811</v>
-      </c>
-      <c r="B89" t="n">
-        <v>99350</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>442432</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7027742</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135574569</v>
-      </c>
-      <c r="B90" t="n">
-        <v>99322</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>222118</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Flugblomster</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Ophrys insectifera</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7027534</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135851787</v>
-      </c>
-      <c r="B91" t="n">
-        <v>104851</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>442360</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7027578</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135851801</v>
-      </c>
-      <c r="B92" t="n">
-        <v>104851</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>442243</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7027546</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135851775</v>
-      </c>
-      <c r="B93" t="n">
-        <v>100354</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>222467</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gräsull</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>442475</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7027687</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>55633849</v>
-      </c>
-      <c r="B94" t="n">
-        <v>101326</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135574547</v>
-      </c>
-      <c r="B95" t="n">
-        <v>101505</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Storbrännan sv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>442418</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7027847</v>
-      </c>
-      <c r="S95" t="n">
-        <v>3</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>5168927</v>
-      </c>
-      <c r="B96" t="n">
-        <v>98137</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>222741</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Finbräken</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Cystopteris montana</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>442283</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7027836</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2001-07-25</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>taxyta Ö1000</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Lisbeth Berntsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135851788</v>
-      </c>
-      <c r="B97" t="n">
-        <v>101428</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>442339</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7027583</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>135851791</v>
-      </c>
-      <c r="B98" t="n">
-        <v>101428</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Alsen-Rödde, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>442312</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7027596</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anton Albertsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -11989,36 +8367,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,10 +4621,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574556</v>
+        <v>135574538</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>58006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442329</v>
+        <v>442449</v>
       </c>
       <c r="R37" t="n">
-        <v>7027573</v>
+        <v>7027722</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,19 +4706,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4737,13 +4737,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574556</t>
+          <t>https://artportalen.se/Sighting/135574538</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135851785</v>
+        <v>135574539</v>
       </c>
       <c r="B38" t="n">
         <v>58006</v>
@@ -4772,19 +4772,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442360</v>
+        <v>442445</v>
       </c>
       <c r="R38" t="n">
-        <v>7027581</v>
+        <v>7027731</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4808,22 +4813,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,24 +4848,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851785</t>
+          <t>https://artportalen.se/Sighting/135574539</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135851790</v>
+        <v>135574540</v>
       </c>
       <c r="B39" t="n">
         <v>58006</v>
@@ -4884,27 +4894,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442323</v>
+        <v>442421</v>
       </c>
       <c r="R39" t="n">
-        <v>7027596</v>
+        <v>7027753</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4928,27 +4935,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,24 +4970,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851790</t>
+          <t>https://artportalen.se/Sighting/135574540</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135851813</v>
+        <v>135574541</v>
       </c>
       <c r="B40" t="n">
         <v>58006</v>
@@ -5009,27 +5016,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442444</v>
+        <v>442414</v>
       </c>
       <c r="R40" t="n">
-        <v>7027735</v>
+        <v>7027802</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5053,27 +5057,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,27 +5092,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851813</t>
+          <t>https://artportalen.se/Sighting/135574541</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135635857</v>
+        <v>135574542</v>
       </c>
       <c r="B41" t="n">
-        <v>58148</v>
+        <v>58006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,34 +5120,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5152,13 +5149,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442366</v>
+        <v>442437</v>
       </c>
       <c r="R41" t="n">
-        <v>7027641</v>
+        <v>7027801</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5185,9 +5182,24 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,58 +5225,59 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135635857</t>
+          <t>https://artportalen.se/Sighting/135574542</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2596274</v>
+        <v>135574544</v>
       </c>
       <c r="B42" t="n">
-        <v>99017</v>
+        <v>58006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442283</v>
+        <v>442430</v>
       </c>
       <c r="R42" t="n">
-        <v>7027836</v>
+        <v>7027816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5288,17 +5301,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,74 +5332,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2596274</t>
+          <t>https://artportalen.se/Sighting/135574544</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574548</v>
+        <v>135574550</v>
       </c>
       <c r="B43" t="n">
-        <v>99297</v>
+        <v>58006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442411</v>
+        <v>442350</v>
       </c>
       <c r="R43" t="n">
-        <v>7027839</v>
+        <v>7027791</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,7 +5428,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5415,7 +5438,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,38 +5469,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574548</t>
+          <t>https://artportalen.se/Sighting/135574550</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574614</v>
+        <v>135574551</v>
       </c>
       <c r="B44" t="n">
-        <v>99297</v>
+        <v>58006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5482,10 +5510,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442464</v>
+        <v>442295</v>
       </c>
       <c r="R44" t="n">
-        <v>7027693</v>
+        <v>7027775</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5517,7 +5545,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5527,7 +5555,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5553,62 +5586,58 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574614</t>
+          <t>https://artportalen.se/Sighting/135574551</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135851773</v>
+        <v>135574553</v>
       </c>
       <c r="B45" t="n">
-        <v>99343</v>
+        <v>58006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442469</v>
+        <v>442327</v>
       </c>
       <c r="R45" t="n">
-        <v>7027704</v>
+        <v>7027590</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5632,22 +5661,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5656,72 +5690,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851773</t>
+          <t>https://artportalen.se/Sighting/135574553</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135851816</v>
+        <v>135574556</v>
       </c>
       <c r="B46" t="n">
-        <v>99343</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442473</v>
+        <v>442329</v>
       </c>
       <c r="R46" t="n">
-        <v>7027780</v>
+        <v>7027573</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5745,29 +5783,34 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bohål, ca 5,5 m upp i tajgagrantickerötad granhögstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5775,62 +5818,67 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851816</t>
+          <t>https://artportalen.se/Sighting/135574556</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574549</v>
+        <v>135574558</v>
       </c>
       <c r="B47" t="n">
-        <v>99319</v>
+        <v>58006</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442411</v>
+        <v>442329</v>
       </c>
       <c r="R47" t="n">
-        <v>7027836</v>
+        <v>7027569</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5862,7 +5910,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5872,7 +5920,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5898,62 +5951,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574549</t>
+          <t>https://artportalen.se/Sighting/135574558</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135851772</v>
+        <v>135574560</v>
       </c>
       <c r="B48" t="n">
-        <v>99365</v>
+        <v>58006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442473</v>
+        <v>442311</v>
       </c>
       <c r="R48" t="n">
-        <v>7027706</v>
+        <v>7027581</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5977,22 +6027,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,72 +6056,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851772</t>
+          <t>https://artportalen.se/Sighting/135574560</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135851793</v>
+        <v>135574561</v>
       </c>
       <c r="B49" t="n">
-        <v>99365</v>
+        <v>58006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442287</v>
+        <v>442291</v>
       </c>
       <c r="R49" t="n">
-        <v>7027599</v>
+        <v>7027577</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6090,22 +6149,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6120,65 +6184,70 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851793</t>
+          <t>https://artportalen.se/Sighting/135574561</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135851800</v>
+        <v>135574575</v>
       </c>
       <c r="B50" t="n">
-        <v>99365</v>
+        <v>58006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442247</v>
+        <v>442296</v>
       </c>
       <c r="R50" t="n">
-        <v>7027546</v>
+        <v>7027551</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6271,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,65 +6306,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851800</t>
+          <t>https://artportalen.se/Sighting/135574575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135851804</v>
+        <v>135574580</v>
       </c>
       <c r="B51" t="n">
-        <v>99365</v>
+        <v>58006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442275</v>
+        <v>442295</v>
       </c>
       <c r="R51" t="n">
-        <v>7027599</v>
+        <v>7027519</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6314,22 +6392,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6344,65 +6427,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851804</t>
+          <t>https://artportalen.se/Sighting/135574580</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135851814</v>
+        <v>135574585</v>
       </c>
       <c r="B52" t="n">
-        <v>99365</v>
+        <v>58006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442453</v>
+        <v>442348</v>
       </c>
       <c r="R52" t="n">
-        <v>7027747</v>
+        <v>7027560</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6426,22 +6513,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6456,65 +6548,70 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851814</t>
+          <t>https://artportalen.se/Sighting/135574585</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135851815</v>
+        <v>135574587</v>
       </c>
       <c r="B53" t="n">
-        <v>99365</v>
+        <v>58006</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442471</v>
+        <v>442355</v>
       </c>
       <c r="R53" t="n">
-        <v>7027763</v>
+        <v>7027577</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,22 +6635,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6568,65 +6670,70 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851815</t>
+          <t>https://artportalen.se/Sighting/135574587</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135851774</v>
+        <v>135574590</v>
       </c>
       <c r="B54" t="n">
-        <v>108436</v>
+        <v>58006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442467</v>
+        <v>442386</v>
       </c>
       <c r="R54" t="n">
-        <v>7027703</v>
+        <v>7027567</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6650,22 +6757,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6680,69 +6792,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851774</t>
+          <t>https://artportalen.se/Sighting/135574590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4041960</v>
+        <v>135574593</v>
       </c>
       <c r="B55" t="n">
-        <v>106229</v>
+        <v>58006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442283</v>
+        <v>442362</v>
       </c>
       <c r="R55" t="n">
-        <v>7027836</v>
+        <v>7027657</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6766,17 +6874,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6787,74 +6905,74 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4041960</t>
+          <t>https://artportalen.se/Sighting/135574593</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135851789</v>
+        <v>135574601</v>
       </c>
       <c r="B56" t="n">
-        <v>106467</v>
+        <v>58006</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442341</v>
+        <v>442387</v>
       </c>
       <c r="R56" t="n">
-        <v>7027597</v>
+        <v>7027641</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6878,22 +6996,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6908,65 +7031,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851789</t>
+          <t>https://artportalen.se/Sighting/135574601</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135851806</v>
+        <v>135574605</v>
       </c>
       <c r="B57" t="n">
-        <v>99363</v>
+        <v>58006</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442315</v>
+        <v>442416</v>
       </c>
       <c r="R57" t="n">
-        <v>7027602</v>
+        <v>7027567</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6990,22 +7113,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7020,65 +7148,70 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851806</t>
+          <t>https://artportalen.se/Sighting/135574605</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135851807</v>
+        <v>135574608</v>
       </c>
       <c r="B58" t="n">
-        <v>99363</v>
+        <v>58006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442368</v>
+        <v>442410</v>
       </c>
       <c r="R58" t="n">
-        <v>7027641</v>
+        <v>7027707</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7102,22 +7235,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7132,65 +7270,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851807</t>
+          <t>https://artportalen.se/Sighting/135574608</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135851811</v>
+        <v>135574610</v>
       </c>
       <c r="B59" t="n">
-        <v>99363</v>
+        <v>58006</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442432</v>
+        <v>442382</v>
       </c>
       <c r="R59" t="n">
-        <v>7027742</v>
+        <v>7027768</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,22 +7352,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,49 +7387,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851811</t>
+          <t>https://artportalen.se/Sighting/135574610</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135574569</v>
+        <v>135574611</v>
       </c>
       <c r="B60" t="n">
-        <v>99322</v>
+        <v>58006</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222118</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7296,10 +7439,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442283</v>
+        <v>442414</v>
       </c>
       <c r="R60" t="n">
-        <v>7027534</v>
+        <v>7027804</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7331,7 +7474,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7341,7 +7484,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7367,54 +7515,59 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574569</t>
+          <t>https://artportalen.se/Sighting/135574611</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135851787</v>
+        <v>135574612</v>
       </c>
       <c r="B61" t="n">
-        <v>104864</v>
+        <v>58006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442360</v>
+        <v>442425</v>
       </c>
       <c r="R61" t="n">
-        <v>7027578</v>
+        <v>7027761</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,22 +7591,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,65 +7626,70 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851787</t>
+          <t>https://artportalen.se/Sighting/135574612</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135851801</v>
+        <v>135574616</v>
       </c>
       <c r="B62" t="n">
-        <v>104864</v>
+        <v>58006</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442243</v>
+        <v>442455</v>
       </c>
       <c r="R62" t="n">
-        <v>7027546</v>
+        <v>7027671</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7550,22 +7713,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7580,65 +7748,70 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851801</t>
+          <t>https://artportalen.se/Sighting/135574616</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135851775</v>
+        <v>135574617</v>
       </c>
       <c r="B63" t="n">
-        <v>100367</v>
+        <v>58006</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222467</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442475</v>
+        <v>442432</v>
       </c>
       <c r="R63" t="n">
-        <v>7027687</v>
+        <v>7027650</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7662,22 +7835,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,74 +7870,70 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851775</t>
+          <t>https://artportalen.se/Sighting/135574617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>55633849</v>
+        <v>135574625</v>
       </c>
       <c r="B64" t="n">
-        <v>101326</v>
+        <v>58006</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442283</v>
+        <v>442465</v>
       </c>
       <c r="R64" t="n">
-        <v>7027836</v>
+        <v>7027665</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7783,17 +7957,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Trakt 19E6a11, taxyta Ö1000</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7804,58 +7988,53 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55633849</t>
+          <t>https://artportalen.se/Sighting/135574625</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135574547</v>
+        <v>135574626</v>
       </c>
       <c r="B65" t="n">
-        <v>101505</v>
+        <v>58006</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7865,10 +8044,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442418</v>
+        <v>442550</v>
       </c>
       <c r="R65" t="n">
-        <v>7027847</v>
+        <v>7027681</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7900,7 +8079,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7910,7 +8089,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7936,58 +8120,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574547</t>
+          <t>https://artportalen.se/Sighting/135574626</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5168927</v>
+        <v>135574627</v>
       </c>
       <c r="B66" t="n">
-        <v>98137</v>
+        <v>58006</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbrännan /700 m SV/, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442283</v>
+        <v>442492</v>
       </c>
       <c r="R66" t="n">
-        <v>7027836</v>
+        <v>7027713</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8011,17 +8191,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2001-07-25</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>taxyta Ö1000</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8032,82 +8222,74 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisbeth Berntsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5168927</t>
+          <t>https://artportalen.se/Sighting/135574627</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135851788</v>
+        <v>135574628</v>
       </c>
       <c r="B67" t="n">
-        <v>101441</v>
+        <v>58006</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Alsen-Rödde, Jmt</t>
+          <t>Storbrännan sv, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442339</v>
+        <v>442502</v>
       </c>
       <c r="R67" t="n">
-        <v>7027583</v>
+        <v>7027719</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8131,22 +8313,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8155,77 +8342,68 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135851788</t>
+          <t>https://artportalen.se/Sighting/135574628</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135851791</v>
+        <v>135851785</v>
       </c>
       <c r="B68" t="n">
-        <v>101441</v>
+        <v>58006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Alsen-Rödde, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442312</v>
+        <v>442360</v>
       </c>
       <c r="R68" t="n">
-        <v>7027596</v>
+        <v>7027581</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8257,7 +8435,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8267,7 +8445,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8276,7 +8454,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8293,6 +8470,3451 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851785</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135851790</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>442323</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851790</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135851813</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>442444</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7027735</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851813</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135635857</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58148</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>442366</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135635857</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2596274</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2596274</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135574548</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99297</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7027839</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574548</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135574614</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99297</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>442464</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7027693</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574614</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135851773</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99343</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>442469</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7027704</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851773</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135851816</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99343</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7027780</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851816</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135574549</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99319</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>442411</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574549</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135851772</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99365</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>442473</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7027706</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851772</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135851793</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99365</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>442287</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851793</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135851800</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99365</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>442247</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851800</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135851804</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99365</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7027599</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851804</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135851814</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99365</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>442453</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7027747</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851814</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135851815</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99365</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>442471</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7027763</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851815</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135851774</v>
+      </c>
+      <c r="B84" t="n">
+        <v>108436</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>442467</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7027703</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851774</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4041960</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4041960</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135851789</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106467</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>442341</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7027597</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851789</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135851806</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99363</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>442315</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7027602</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851806</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135851807</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99363</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>442368</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7027641</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851807</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135851811</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99363</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>442432</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7027742</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851811</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135574569</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99322</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7027534</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574569</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135851787</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104864</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>442360</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7027578</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851787</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135851801</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104864</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>442243</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7027546</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851801</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135851775</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100367</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>442475</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7027687</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851775</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>55633849</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Trakt 19E6a11, taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55633849</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135574547</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Storbrännan sv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>442418</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7027847</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574547</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5168927</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Storbrännan /700 m SV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>442283</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7027836</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2001-07-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lisbeth Berntsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5168927</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135851788</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101441</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>442339</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7027583</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135851788</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135851791</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101441</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Alsen-Rödde, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>442312</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7027596</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135851791</t>
         </is>
@@ -8367,6 +11989,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28723-2026 artfynd.xlsx
+++ b/artfynd/A 28723-2026 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>135851779</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135851777</v>
       </c>
       <c r="B17" t="n">
-        <v>96556</v>
+        <v>96557</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>135851783</v>
       </c>
       <c r="B18" t="n">
-        <v>96556</v>
+        <v>96557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>135851819</v>
       </c>
       <c r="B19" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135851771</v>
       </c>
       <c r="B20" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135851809</v>
       </c>
       <c r="B21" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>135851798</v>
       </c>
       <c r="B22" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135851770</v>
       </c>
       <c r="B24" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135851769</v>
       </c>
       <c r="B26" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>135851796</v>
       </c>
       <c r="B27" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135851799</v>
       </c>
       <c r="B28" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135851780</v>
       </c>
       <c r="B29" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135851784</v>
       </c>
       <c r="B30" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>135851792</v>
       </c>
       <c r="B31" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135851795</v>
       </c>
       <c r="B32" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135851802</v>
       </c>
       <c r="B33" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135851805</v>
       </c>
       <c r="B34" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135851812</v>
       </c>
       <c r="B35" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>135851808</v>
       </c>
       <c r="B36" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135851773</v>
       </c>
       <c r="B75" t="n">
-        <v>99343</v>
+        <v>99344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>135851816</v>
       </c>
       <c r="B76" t="n">
-        <v>99343</v>
+        <v>99344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>135851772</v>
       </c>
       <c r="B78" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135851793</v>
       </c>
       <c r="B79" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>135851800</v>
       </c>
       <c r="B80" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>135851804</v>
       </c>
       <c r="B81" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135851814</v>
       </c>
       <c r="B82" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135851815</v>
       </c>
       <c r="B83" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135851774</v>
       </c>
       <c r="B84" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>135851789</v>
       </c>
       <c r="B86" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>135851806</v>
       </c>
       <c r="B87" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>135851807</v>
       </c>
       <c r="B88" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>135851811</v>
       </c>
       <c r="B89" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>135851787</v>
       </c>
       <c r="B91" t="n">
-        <v>104864</v>
+        <v>104865</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135851801</v>
       </c>
       <c r="B92" t="n">
-        <v>104864</v>
+        <v>104865</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>135851775</v>
       </c>
       <c r="B93" t="n">
-        <v>100367</v>
+        <v>100368</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>135851788</v>
       </c>
       <c r="B97" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>135851791</v>
       </c>
       <c r="B98" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
